--- a/app/templates/informes/ControlTemperaturas/F-LEM-IN-01.02 V03 FORMATO DE VERIFICACIÓN DIARIA DE BALANZAS.xlsx
+++ b/app/templates/informes/ControlTemperaturas/F-LEM-IN-01.02 V03 FORMATO DE VERIFICACIÓN DIARIA DE BALANZAS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\crmnew\api-geofal-crm\app\templates\informes\ControlTemperaturas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ACEC94A7-78B3-4A90-8EE7-B3F64A644526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CB2BA28-99AA-492B-8A0A-749BDC954026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{75FE1682-50EA-475C-BED2-B385DB22473E}"/>
   </bookViews>
@@ -197,10 +197,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="214" formatCode="\L\ \-\ 0000"/>
-    <numFmt numFmtId="215" formatCode="dd\-mmm\-yyyy"/>
-    <numFmt numFmtId="224" formatCode="&quot;0&quot;0"/>
-    <numFmt numFmtId="226" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="\L\ \-\ 0000"/>
+    <numFmt numFmtId="165" formatCode="dd\-mmm\-yyyy"/>
+    <numFmt numFmtId="166" formatCode="&quot;0&quot;0"/>
+    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="31" x14ac:knownFonts="1">
     <font>
@@ -685,85 +685,75 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="141">
+  <cellXfs count="134">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="214" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="215" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="3" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -788,79 +778,72 @@
     <xf numFmtId="0" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="224" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="215" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -901,10 +884,10 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -916,30 +899,23 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="226" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
@@ -986,10 +962,28 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="215" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection hidden="1"/>
     </xf>
@@ -1005,7 +999,7 @@
     <xf numFmtId="0" fontId="26" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1014,32 +1008,28 @@
     <xf numFmtId="0" fontId="26" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="2" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="2" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1049,13 +1039,19 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1073,7 +1069,7 @@
     <xf numFmtId="0" fontId="28" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1090,10 +1086,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1107,34 +1099,18 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2234,68 +2210,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="96"/>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="97" t="s">
+      <c r="A1" s="95"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="96" t="s">
         <v>30</v>
       </c>
-      <c r="E1" s="98"/>
-      <c r="F1" s="98"/>
-      <c r="G1" s="98"/>
-      <c r="H1" s="98"/>
-      <c r="I1" s="98"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="97"/>
+      <c r="G1" s="97"/>
+      <c r="H1" s="97"/>
+      <c r="I1" s="97"/>
       <c r="J1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="K1" s="35" t="s">
+      <c r="K1" s="31" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="96"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
-      <c r="D2" s="99"/>
-      <c r="E2" s="100"/>
-      <c r="F2" s="100"/>
-      <c r="G2" s="100"/>
-      <c r="H2" s="100"/>
-      <c r="I2" s="100"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
       <c r="J2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="K2" s="36">
+      <c r="K2" s="32">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="96"/>
-      <c r="B3" s="96"/>
-      <c r="C3" s="96"/>
-      <c r="D3" s="99"/>
-      <c r="E3" s="100"/>
-      <c r="F3" s="100"/>
-      <c r="G3" s="100"/>
-      <c r="H3" s="100"/>
-      <c r="I3" s="100"/>
+      <c r="A3" s="95"/>
+      <c r="B3" s="95"/>
+      <c r="C3" s="95"/>
+      <c r="D3" s="98"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="99"/>
+      <c r="G3" s="99"/>
+      <c r="H3" s="99"/>
+      <c r="I3" s="99"/>
       <c r="J3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="K3" s="37">
+      <c r="K3" s="33">
         <v>44319</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="96"/>
-      <c r="B4" s="96"/>
-      <c r="C4" s="96"/>
-      <c r="D4" s="101"/>
-      <c r="E4" s="102"/>
-      <c r="F4" s="102"/>
-      <c r="G4" s="102"/>
-      <c r="H4" s="102"/>
-      <c r="I4" s="102"/>
+      <c r="A4" s="95"/>
+      <c r="B4" s="95"/>
+      <c r="C4" s="95"/>
+      <c r="D4" s="100"/>
+      <c r="E4" s="101"/>
+      <c r="F4" s="101"/>
+      <c r="G4" s="101"/>
+      <c r="H4" s="101"/>
+      <c r="I4" s="101"/>
       <c r="J4" s="1" t="s">
         <v>2</v>
       </c>
@@ -2320,494 +2296,494 @@
       <c r="A6" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="22"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="23"/>
-      <c r="I6" s="106"/>
-      <c r="J6" s="107"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="90"/>
+      <c r="J6" s="90"/>
       <c r="K6" s="20"/>
     </row>
     <row r="7" spans="1:18" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="33" t="s">
+      <c r="A7" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="34"/>
-      <c r="C7" s="94"/>
-      <c r="D7" s="94"/>
-      <c r="E7" s="94"/>
-      <c r="F7" s="94"/>
-      <c r="G7" s="94"/>
-      <c r="H7" s="94"/>
-      <c r="I7" s="94"/>
-      <c r="J7" s="94"/>
-      <c r="K7" s="94"/>
+      <c r="B7" s="30"/>
+      <c r="C7" s="93"/>
+      <c r="D7" s="93"/>
+      <c r="E7" s="93"/>
+      <c r="F7" s="93"/>
+      <c r="G7" s="93"/>
+      <c r="H7" s="93"/>
+      <c r="I7" s="93"/>
+      <c r="J7" s="93"/>
+      <c r="K7" s="93"/>
     </row>
     <row r="8" spans="1:18" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="33" t="s">
+      <c r="A8" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="34"/>
-      <c r="C8" s="94"/>
-      <c r="D8" s="94"/>
-      <c r="E8" s="94"/>
-      <c r="F8" s="94"/>
-      <c r="G8" s="94"/>
-      <c r="H8" s="94"/>
-      <c r="I8" s="94"/>
-      <c r="J8" s="94"/>
-      <c r="K8" s="94"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="93"/>
+      <c r="D8" s="93"/>
+      <c r="E8" s="93"/>
+      <c r="F8" s="93"/>
+      <c r="G8" s="93"/>
+      <c r="H8" s="93"/>
+      <c r="I8" s="93"/>
+      <c r="J8" s="93"/>
+      <c r="K8" s="93"/>
       <c r="O8" s="8"/>
       <c r="P8" s="8"/>
       <c r="Q8" s="6"/>
       <c r="R8" s="2"/>
     </row>
     <row r="9" spans="1:18" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="33" t="s">
+      <c r="A9" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="34"/>
-      <c r="C9" s="94"/>
-      <c r="D9" s="94"/>
-      <c r="E9" s="94"/>
-      <c r="F9" s="94"/>
-      <c r="G9" s="94"/>
-      <c r="H9" s="94"/>
-      <c r="I9" s="94"/>
-      <c r="J9" s="94"/>
-      <c r="K9" s="94"/>
+      <c r="B9" s="30"/>
+      <c r="C9" s="93"/>
+      <c r="D9" s="93"/>
+      <c r="E9" s="93"/>
+      <c r="F9" s="93"/>
+      <c r="G9" s="93"/>
+      <c r="H9" s="93"/>
+      <c r="I9" s="93"/>
+      <c r="J9" s="93"/>
+      <c r="K9" s="93"/>
       <c r="O9" s="8"/>
       <c r="P9" s="8"/>
-      <c r="Q9" s="95"/>
-      <c r="R9" s="95"/>
+      <c r="Q9" s="94"/>
+      <c r="R9" s="94"/>
     </row>
     <row r="10" spans="1:18" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="33" t="s">
+      <c r="A10" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="34"/>
-      <c r="C10" s="94"/>
-      <c r="D10" s="94"/>
-      <c r="E10" s="94"/>
-      <c r="F10" s="94"/>
-      <c r="G10" s="94"/>
-      <c r="H10" s="94"/>
-      <c r="I10" s="94"/>
-      <c r="J10" s="94"/>
-      <c r="K10" s="94"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="93"/>
+      <c r="D10" s="93"/>
+      <c r="E10" s="93"/>
+      <c r="F10" s="93"/>
+      <c r="G10" s="93"/>
+      <c r="H10" s="93"/>
+      <c r="I10" s="93"/>
+      <c r="J10" s="93"/>
+      <c r="K10" s="93"/>
       <c r="O10" s="8"/>
       <c r="P10" s="8"/>
       <c r="Q10" s="19"/>
       <c r="R10" s="19"/>
     </row>
     <row r="11" spans="1:18" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="33" t="s">
+      <c r="A11" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="34"/>
-      <c r="C11" s="94"/>
-      <c r="D11" s="94"/>
-      <c r="E11" s="94"/>
-      <c r="F11" s="94"/>
-      <c r="G11" s="94"/>
-      <c r="H11" s="94"/>
-      <c r="I11" s="94"/>
-      <c r="J11" s="94"/>
-      <c r="K11" s="94"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="93"/>
+      <c r="D11" s="93"/>
+      <c r="E11" s="93"/>
+      <c r="F11" s="93"/>
+      <c r="G11" s="93"/>
+      <c r="H11" s="93"/>
+      <c r="I11" s="93"/>
+      <c r="J11" s="93"/>
+      <c r="K11" s="93"/>
       <c r="O11" s="8"/>
       <c r="P11" s="8"/>
       <c r="Q11" s="19"/>
       <c r="R11" s="19"/>
     </row>
     <row r="12" spans="1:18" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="33" t="s">
+      <c r="A12" s="20" t="s">
         <v>3</v>
       </c>
       <c r="B12" s="20"/>
-      <c r="C12" s="94"/>
-      <c r="D12" s="94"/>
-      <c r="E12" s="94"/>
-      <c r="F12" s="94"/>
-      <c r="G12" s="94"/>
-      <c r="H12" s="94"/>
-      <c r="I12" s="94"/>
-      <c r="J12" s="94"/>
-      <c r="K12" s="94"/>
+      <c r="C12" s="93"/>
+      <c r="D12" s="93"/>
+      <c r="E12" s="93"/>
+      <c r="F12" s="93"/>
+      <c r="G12" s="93"/>
+      <c r="H12" s="93"/>
+      <c r="I12" s="93"/>
+      <c r="J12" s="93"/>
+      <c r="K12" s="93"/>
       <c r="O12" s="8"/>
       <c r="P12" s="8"/>
       <c r="Q12" s="19"/>
       <c r="R12" s="19"/>
     </row>
     <row r="13" spans="1:18" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="33" t="s">
+      <c r="A13" s="20" t="s">
         <v>0</v>
       </c>
       <c r="B13" s="20"/>
-      <c r="C13" s="94"/>
-      <c r="D13" s="94"/>
-      <c r="E13" s="94"/>
-      <c r="F13" s="94"/>
-      <c r="G13" s="94"/>
-      <c r="H13" s="94"/>
-      <c r="I13" s="94"/>
-      <c r="J13" s="94"/>
-      <c r="K13" s="94"/>
+      <c r="C13" s="93"/>
+      <c r="D13" s="93"/>
+      <c r="E13" s="93"/>
+      <c r="F13" s="93"/>
+      <c r="G13" s="93"/>
+      <c r="H13" s="93"/>
+      <c r="I13" s="93"/>
+      <c r="J13" s="93"/>
+      <c r="K13" s="93"/>
       <c r="O13" s="8"/>
       <c r="P13" s="8"/>
       <c r="Q13" s="19"/>
       <c r="R13" s="19"/>
     </row>
     <row r="14" spans="1:18" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="33" t="s">
+      <c r="A14" s="20" t="s">
         <v>37</v>
       </c>
       <c r="B14" s="20"/>
-      <c r="C14" s="65"/>
-      <c r="D14" s="66"/>
-      <c r="E14" s="66"/>
-      <c r="F14" s="66"/>
-      <c r="G14" s="66"/>
-      <c r="H14" s="66" t="s">
+      <c r="C14" s="60"/>
+      <c r="D14" s="61"/>
+      <c r="E14" s="61"/>
+      <c r="F14" s="61"/>
+      <c r="G14" s="61"/>
+      <c r="H14" s="61" t="s">
         <v>39</v>
       </c>
-      <c r="I14" s="66"/>
-      <c r="J14" s="67"/>
-      <c r="K14" s="68"/>
+      <c r="I14" s="61"/>
+      <c r="J14" s="62"/>
+      <c r="K14" s="63"/>
       <c r="O14" s="8"/>
       <c r="P14" s="8"/>
       <c r="Q14" s="19"/>
       <c r="R14" s="19"/>
     </row>
     <row r="15" spans="1:18" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A15" s="25"/>
-      <c r="B15" s="25"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="25"/>
-      <c r="I15" s="25"/>
-      <c r="J15" s="25"/>
-      <c r="K15" s="25"/>
+      <c r="A15" s="22"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="22"/>
+      <c r="K15" s="22"/>
       <c r="O15" s="8"/>
       <c r="P15" s="8"/>
       <c r="Q15" s="19"/>
       <c r="R15" s="19"/>
     </row>
     <row r="16" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="58"/>
-      <c r="B16" s="59"/>
-      <c r="C16" s="59"/>
-      <c r="D16" s="59"/>
-      <c r="E16" s="59"/>
-      <c r="F16" s="59"/>
-      <c r="G16" s="59"/>
-      <c r="H16" s="59"/>
-      <c r="I16" s="59"/>
-      <c r="J16" s="59"/>
-      <c r="K16" s="60"/>
+      <c r="A16" s="53"/>
+      <c r="B16" s="54"/>
+      <c r="C16" s="54"/>
+      <c r="D16" s="54"/>
+      <c r="E16" s="54"/>
+      <c r="F16" s="54"/>
+      <c r="G16" s="54"/>
+      <c r="H16" s="54"/>
+      <c r="I16" s="54"/>
+      <c r="J16" s="54"/>
+      <c r="K16" s="55"/>
       <c r="O16" s="8"/>
       <c r="P16" s="8"/>
       <c r="Q16" s="19"/>
       <c r="R16" s="19"/>
     </row>
     <row r="17" spans="1:18" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="61"/>
+      <c r="A17" s="56"/>
       <c r="B17" s="20"/>
-      <c r="C17" s="26" t="s">
+      <c r="C17" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="27" t="s">
+      <c r="D17" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="E17" s="27" t="s">
+      <c r="E17" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="F17" s="26" t="s">
+      <c r="F17" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="G17" s="26" t="s">
+      <c r="G17" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="H17" s="27" t="s">
+      <c r="H17" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="I17" s="27" t="s">
+      <c r="I17" s="24" t="s">
         <v>18</v>
       </c>
       <c r="J17" s="20"/>
-      <c r="K17" s="62"/>
+      <c r="K17" s="57"/>
       <c r="O17" s="8"/>
       <c r="P17" s="8"/>
       <c r="Q17" s="19"/>
       <c r="R17" s="19"/>
     </row>
     <row r="18" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="61"/>
+      <c r="A18" s="56"/>
       <c r="B18" s="20"/>
-      <c r="C18" s="28">
+      <c r="C18" s="25">
         <v>5</v>
       </c>
-      <c r="D18" s="29">
+      <c r="D18" s="26">
         <v>5</v>
       </c>
-      <c r="E18" s="29">
+      <c r="E18" s="26">
         <v>5</v>
       </c>
-      <c r="F18" s="29">
+      <c r="F18" s="26">
         <f t="shared" ref="F18:F25" si="0">C18-D18</f>
         <v>0</v>
       </c>
-      <c r="G18" s="29">
+      <c r="G18" s="26">
         <f t="shared" ref="G18:G25" si="1">C18-E18</f>
         <v>0</v>
       </c>
-      <c r="H18" s="30">
+      <c r="H18" s="27">
         <v>0.1</v>
       </c>
-      <c r="I18" s="31" t="s">
+      <c r="I18" s="28" t="s">
         <v>8</v>
       </c>
       <c r="J18" s="20"/>
-      <c r="K18" s="62"/>
+      <c r="K18" s="57"/>
       <c r="O18" s="8"/>
       <c r="P18" s="8"/>
       <c r="Q18" s="19"/>
       <c r="R18" s="19"/>
     </row>
     <row r="19" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="61"/>
+      <c r="A19" s="56"/>
       <c r="B19" s="20"/>
-      <c r="C19" s="28">
+      <c r="C19" s="25">
         <v>20</v>
       </c>
-      <c r="D19" s="29">
+      <c r="D19" s="26">
         <v>20.010000000000002</v>
       </c>
-      <c r="E19" s="29">
+      <c r="E19" s="26">
         <v>20.010000000000002</v>
       </c>
-      <c r="F19" s="29">
+      <c r="F19" s="26">
         <f t="shared" si="0"/>
         <v>-1.0000000000001563E-2</v>
       </c>
-      <c r="G19" s="29">
+      <c r="G19" s="26">
         <f t="shared" si="1"/>
         <v>-1.0000000000001563E-2</v>
       </c>
-      <c r="H19" s="30">
+      <c r="H19" s="27">
         <v>0.1</v>
       </c>
-      <c r="I19" s="31" t="s">
+      <c r="I19" s="28" t="s">
         <v>8</v>
       </c>
       <c r="J19" s="20"/>
-      <c r="K19" s="62"/>
+      <c r="K19" s="57"/>
       <c r="O19" s="8"/>
       <c r="P19" s="8"/>
       <c r="Q19" s="19"/>
       <c r="R19" s="19"/>
     </row>
     <row r="20" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="61"/>
+      <c r="A20" s="56"/>
       <c r="B20" s="20"/>
-      <c r="C20" s="28">
+      <c r="C20" s="25">
         <v>100</v>
       </c>
-      <c r="D20" s="29">
+      <c r="D20" s="26">
         <v>100.01</v>
       </c>
-      <c r="E20" s="29">
+      <c r="E20" s="26">
         <v>100</v>
       </c>
-      <c r="F20" s="29">
+      <c r="F20" s="26">
         <f t="shared" si="0"/>
         <v>-1.0000000000005116E-2</v>
       </c>
-      <c r="G20" s="29">
+      <c r="G20" s="26">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H20" s="30">
+      <c r="H20" s="27">
         <v>0.1</v>
       </c>
-      <c r="I20" s="31" t="s">
+      <c r="I20" s="28" t="s">
         <v>8</v>
       </c>
       <c r="J20" s="20"/>
-      <c r="K20" s="62"/>
+      <c r="K20" s="57"/>
       <c r="O20" s="8"/>
       <c r="P20" s="8"/>
       <c r="Q20" s="19"/>
       <c r="R20" s="19"/>
     </row>
     <row r="21" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="61"/>
+      <c r="A21" s="56"/>
       <c r="B21" s="20"/>
-      <c r="C21" s="28">
+      <c r="C21" s="25">
         <v>200</v>
       </c>
-      <c r="D21" s="29">
+      <c r="D21" s="26">
         <v>199.99</v>
       </c>
-      <c r="E21" s="29">
+      <c r="E21" s="26">
         <v>199.99</v>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="26">
         <f t="shared" si="0"/>
         <v>9.9999999999909051E-3</v>
       </c>
-      <c r="G21" s="29">
+      <c r="G21" s="26">
         <f t="shared" si="1"/>
         <v>9.9999999999909051E-3</v>
       </c>
-      <c r="H21" s="30">
+      <c r="H21" s="27">
         <v>0.1</v>
       </c>
-      <c r="I21" s="31" t="s">
+      <c r="I21" s="28" t="s">
         <v>8</v>
       </c>
       <c r="J21" s="20"/>
-      <c r="K21" s="62"/>
+      <c r="K21" s="57"/>
       <c r="O21" s="8"/>
       <c r="P21" s="8"/>
       <c r="Q21" s="19"/>
       <c r="R21" s="19"/>
     </row>
     <row r="22" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="61"/>
+      <c r="A22" s="56"/>
       <c r="B22" s="20"/>
-      <c r="C22" s="28">
+      <c r="C22" s="25">
         <v>500</v>
       </c>
-      <c r="D22" s="29">
+      <c r="D22" s="26">
         <v>500.02</v>
       </c>
-      <c r="E22" s="29">
+      <c r="E22" s="26">
         <v>500.01</v>
       </c>
-      <c r="F22" s="29">
+      <c r="F22" s="26">
         <f t="shared" si="0"/>
         <v>-1.999999999998181E-2</v>
       </c>
-      <c r="G22" s="29">
+      <c r="G22" s="26">
         <f t="shared" si="1"/>
         <v>-9.9999999999909051E-3</v>
       </c>
-      <c r="H22" s="30">
+      <c r="H22" s="27">
         <v>0.1</v>
       </c>
-      <c r="I22" s="31" t="s">
+      <c r="I22" s="28" t="s">
         <v>8</v>
       </c>
       <c r="J22" s="20"/>
-      <c r="K22" s="62"/>
+      <c r="K22" s="57"/>
       <c r="O22" s="8"/>
       <c r="P22" s="8"/>
       <c r="Q22" s="19"/>
       <c r="R22" s="19"/>
     </row>
     <row r="23" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="61"/>
+      <c r="A23" s="56"/>
       <c r="B23" s="20"/>
-      <c r="C23" s="28">
+      <c r="C23" s="25">
         <v>1000</v>
       </c>
-      <c r="D23" s="29">
+      <c r="D23" s="26">
         <v>1000.01</v>
       </c>
-      <c r="E23" s="29">
+      <c r="E23" s="26">
         <v>1000.01</v>
       </c>
-      <c r="F23" s="29">
+      <c r="F23" s="26">
         <f t="shared" si="0"/>
         <v>-9.9999999999909051E-3</v>
       </c>
-      <c r="G23" s="29">
+      <c r="G23" s="26">
         <f t="shared" si="1"/>
         <v>-9.9999999999909051E-3</v>
       </c>
-      <c r="H23" s="30">
+      <c r="H23" s="27">
         <v>0.1</v>
       </c>
-      <c r="I23" s="31" t="s">
+      <c r="I23" s="28" t="s">
         <v>8</v>
       </c>
       <c r="J23" s="20"/>
-      <c r="K23" s="62"/>
+      <c r="K23" s="57"/>
     </row>
     <row r="24" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="61"/>
+      <c r="A24" s="56"/>
       <c r="B24" s="20"/>
-      <c r="C24" s="28">
+      <c r="C24" s="25">
         <v>2000</v>
       </c>
-      <c r="D24" s="29">
+      <c r="D24" s="26">
         <v>2000.01</v>
       </c>
-      <c r="E24" s="29">
+      <c r="E24" s="26">
         <v>2000.01</v>
       </c>
-      <c r="F24" s="29">
+      <c r="F24" s="26">
         <f t="shared" si="0"/>
         <v>-9.9999999999909051E-3</v>
       </c>
-      <c r="G24" s="29">
+      <c r="G24" s="26">
         <f t="shared" si="1"/>
         <v>-9.9999999999909051E-3</v>
       </c>
-      <c r="H24" s="30">
+      <c r="H24" s="27">
         <v>0.1</v>
       </c>
-      <c r="I24" s="31" t="s">
+      <c r="I24" s="28" t="s">
         <v>8</v>
       </c>
       <c r="J24" s="20"/>
-      <c r="K24" s="62"/>
+      <c r="K24" s="57"/>
       <c r="O24" s="8"/>
       <c r="P24" s="8"/>
       <c r="Q24" s="19"/>
       <c r="R24" s="19"/>
     </row>
     <row r="25" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="61"/>
+      <c r="A25" s="56"/>
       <c r="B25" s="20"/>
-      <c r="C25" s="28">
+      <c r="C25" s="25">
         <v>5000</v>
       </c>
-      <c r="D25" s="29">
+      <c r="D25" s="26">
         <v>5000.1000000000004</v>
       </c>
-      <c r="E25" s="29">
+      <c r="E25" s="26">
         <v>5000.09</v>
       </c>
-      <c r="F25" s="29">
+      <c r="F25" s="26">
         <f t="shared" si="0"/>
         <v>-0.1000000000003638</v>
       </c>
-      <c r="G25" s="29">
+      <c r="G25" s="26">
         <f t="shared" si="1"/>
         <v>-9.0000000000145519E-2</v>
       </c>
-      <c r="H25" s="30">
+      <c r="H25" s="27">
         <v>0.1</v>
       </c>
-      <c r="I25" s="31" t="s">
+      <c r="I25" s="28" t="s">
         <v>8</v>
       </c>
       <c r="J25" s="20"/>
-      <c r="K25" s="62"/>
+      <c r="K25" s="57"/>
       <c r="O25" s="8"/>
       <c r="P25" s="8"/>
       <c r="Q25" s="19"/>
       <c r="R25" s="19"/>
     </row>
     <row r="26" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="61"/>
+      <c r="A26" s="56"/>
       <c r="B26" s="20"/>
       <c r="C26" s="20"/>
       <c r="D26" s="20"/>
@@ -2817,78 +2793,78 @@
       <c r="H26" s="20"/>
       <c r="I26" s="20"/>
       <c r="J26" s="20"/>
-      <c r="K26" s="62"/>
+      <c r="K26" s="57"/>
       <c r="O26" s="8"/>
       <c r="P26" s="8"/>
       <c r="Q26" s="19"/>
       <c r="R26" s="19"/>
     </row>
     <row r="27" spans="1:18" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="103" t="s">
+      <c r="A27" s="87" t="s">
         <v>19</v>
       </c>
-      <c r="B27" s="104"/>
-      <c r="C27" s="32" t="s">
+      <c r="B27" s="88"/>
+      <c r="C27" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="D27" s="32" t="s">
+      <c r="D27" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="E27" s="32" t="s">
+      <c r="E27" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="32" t="s">
+      <c r="F27" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="G27" s="32" t="s">
+      <c r="G27" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="H27" s="32" t="s">
+      <c r="H27" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="I27" s="32" t="s">
+      <c r="I27" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="J27" s="32" t="s">
+      <c r="J27" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="K27" s="62"/>
+      <c r="K27" s="57"/>
       <c r="O27" s="8"/>
       <c r="P27" s="8"/>
       <c r="Q27" s="19"/>
       <c r="R27" s="19"/>
     </row>
     <row r="28" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="108" t="s">
+      <c r="A28" s="91" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="109"/>
-      <c r="C28" s="38"/>
-      <c r="D28" s="38"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="38"/>
-      <c r="H28" s="38"/>
-      <c r="I28" s="38"/>
-      <c r="J28" s="38"/>
-      <c r="K28" s="62"/>
+      <c r="B28" s="92"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="34"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="34"/>
+      <c r="K28" s="57"/>
       <c r="O28" s="8"/>
       <c r="P28" s="8"/>
       <c r="Q28" s="19"/>
       <c r="R28" s="19"/>
     </row>
     <row r="29" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="63"/>
-      <c r="B29" s="25"/>
+      <c r="A29" s="58"/>
+      <c r="B29" s="22"/>
       <c r="C29" s="18"/>
       <c r="D29" s="18"/>
-      <c r="E29" s="25"/>
-      <c r="F29" s="25"/>
-      <c r="G29" s="25"/>
-      <c r="H29" s="25"/>
-      <c r="I29" s="25"/>
-      <c r="J29" s="25"/>
-      <c r="K29" s="64"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="22"/>
+      <c r="H29" s="22"/>
+      <c r="I29" s="22"/>
+      <c r="J29" s="22"/>
+      <c r="K29" s="59"/>
       <c r="O29" s="8"/>
       <c r="P29" s="8"/>
       <c r="Q29" s="19"/>
@@ -2906,26 +2882,26 @@
       <c r="K30" s="20"/>
       <c r="O30" s="8"/>
       <c r="P30" s="8"/>
-      <c r="Q30" s="47"/>
-      <c r="R30" s="47"/>
+      <c r="Q30" s="19"/>
+      <c r="R30" s="19"/>
     </row>
     <row r="31" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="57" t="s">
+      <c r="A31" s="52" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="59"/>
-      <c r="C31" s="39"/>
-      <c r="D31" s="39"/>
-      <c r="E31" s="59"/>
-      <c r="F31" s="59"/>
-      <c r="G31" s="59"/>
-      <c r="H31" s="59"/>
-      <c r="I31" s="59"/>
-      <c r="J31" s="59"/>
-      <c r="K31" s="60"/>
+      <c r="B31" s="54"/>
+      <c r="C31" s="35"/>
+      <c r="D31" s="35"/>
+      <c r="E31" s="54"/>
+      <c r="F31" s="54"/>
+      <c r="G31" s="54"/>
+      <c r="H31" s="54"/>
+      <c r="I31" s="54"/>
+      <c r="J31" s="54"/>
+      <c r="K31" s="55"/>
     </row>
     <row r="32" spans="1:18" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="61"/>
+      <c r="A32" s="56"/>
       <c r="B32" s="20"/>
       <c r="C32" s="20"/>
       <c r="D32" s="20"/>
@@ -2935,10 +2911,10 @@
       <c r="H32" s="20"/>
       <c r="I32" s="20"/>
       <c r="J32" s="20"/>
-      <c r="K32" s="62"/>
+      <c r="K32" s="57"/>
     </row>
     <row r="33" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="61"/>
+      <c r="A33" s="56"/>
       <c r="B33" s="20"/>
       <c r="C33" s="20"/>
       <c r="D33" s="20"/>
@@ -2948,10 +2924,10 @@
       <c r="H33" s="20"/>
       <c r="I33" s="20"/>
       <c r="J33" s="20"/>
-      <c r="K33" s="62"/>
+      <c r="K33" s="57"/>
     </row>
     <row r="34" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="61"/>
+      <c r="A34" s="56"/>
       <c r="B34" s="20"/>
       <c r="C34" s="20"/>
       <c r="D34" s="20"/>
@@ -2961,20 +2937,20 @@
       <c r="H34" s="20"/>
       <c r="I34" s="20"/>
       <c r="J34" s="20"/>
-      <c r="K34" s="62"/>
+      <c r="K34" s="57"/>
     </row>
     <row r="35" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="63"/>
-      <c r="B35" s="25"/>
-      <c r="C35" s="25"/>
-      <c r="D35" s="25"/>
-      <c r="E35" s="25"/>
-      <c r="F35" s="25"/>
-      <c r="G35" s="25"/>
-      <c r="H35" s="25"/>
-      <c r="I35" s="25"/>
-      <c r="J35" s="25"/>
-      <c r="K35" s="64"/>
+      <c r="A35" s="58"/>
+      <c r="B35" s="22"/>
+      <c r="C35" s="22"/>
+      <c r="D35" s="22"/>
+      <c r="E35" s="22"/>
+      <c r="F35" s="22"/>
+      <c r="G35" s="22"/>
+      <c r="H35" s="22"/>
+      <c r="I35" s="22"/>
+      <c r="J35" s="22"/>
+      <c r="K35" s="59"/>
     </row>
     <row r="36" spans="1:11" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A36" s="20"/>
@@ -3054,19 +3030,19 @@
       <c r="B43" s="12"/>
     </row>
     <row r="44" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="105" t="s">
+      <c r="A44" s="89" t="s">
         <v>5</v>
       </c>
-      <c r="B44" s="105"/>
-      <c r="C44" s="105"/>
-      <c r="D44" s="105"/>
-      <c r="E44" s="105"/>
-      <c r="F44" s="105"/>
-      <c r="G44" s="105"/>
-      <c r="H44" s="105"/>
-      <c r="I44" s="105"/>
-      <c r="J44" s="105"/>
-      <c r="K44" s="105"/>
+      <c r="B44" s="89"/>
+      <c r="C44" s="89"/>
+      <c r="D44" s="89"/>
+      <c r="E44" s="89"/>
+      <c r="F44" s="89"/>
+      <c r="G44" s="89"/>
+      <c r="H44" s="89"/>
+      <c r="I44" s="89"/>
+      <c r="J44" s="89"/>
+      <c r="K44" s="89"/>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="9"/>
@@ -3074,6 +3050,9 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="Q9:R9"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:I4"/>
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="A44:K44"/>
     <mergeCell ref="I6:J6"/>
@@ -3085,9 +3064,6 @@
     <mergeCell ref="C12:K12"/>
     <mergeCell ref="C13:K13"/>
     <mergeCell ref="C7:K7"/>
-    <mergeCell ref="Q9:R9"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:I4"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.78740157480314965" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0" footer="0"/>
@@ -3109,7 +3085,7 @@
     <col min="3" max="3" width="6" style="4" customWidth="1"/>
     <col min="4" max="4" width="7.6640625" style="4" customWidth="1"/>
     <col min="5" max="5" width="14.88671875" style="4" customWidth="1"/>
-    <col min="6" max="6" width="11.88671875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="34.6640625" style="4" customWidth="1"/>
     <col min="7" max="7" width="15.6640625" style="4" customWidth="1"/>
     <col min="8" max="8" width="7.88671875" style="4" customWidth="1"/>
     <col min="9" max="9" width="15.6640625" style="4" customWidth="1"/>
@@ -3146,136 +3122,136 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="96"/>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="127"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="118" t="s">
+      <c r="A1" s="95"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="126"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="117" t="s">
         <v>31</v>
       </c>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
-      <c r="AC1" s="119"/>
-      <c r="AD1" s="119"/>
-      <c r="AE1" s="119"/>
-      <c r="AF1" s="119"/>
-      <c r="AG1" s="119"/>
-      <c r="AH1" s="119"/>
-      <c r="AI1" s="119"/>
-      <c r="AJ1" s="120"/>
+      <c r="G1" s="118"/>
+      <c r="H1" s="118"/>
+      <c r="I1" s="118"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="118"/>
+      <c r="T1" s="118"/>
+      <c r="U1" s="118"/>
+      <c r="V1" s="118"/>
+      <c r="W1" s="118"/>
+      <c r="X1" s="118"/>
+      <c r="Y1" s="118"/>
+      <c r="Z1" s="118"/>
+      <c r="AA1" s="118"/>
+      <c r="AB1" s="118"/>
+      <c r="AC1" s="118"/>
+      <c r="AD1" s="118"/>
+      <c r="AE1" s="118"/>
+      <c r="AF1" s="118"/>
+      <c r="AG1" s="118"/>
+      <c r="AH1" s="118"/>
+      <c r="AI1" s="118"/>
+      <c r="AJ1" s="119"/>
       <c r="AK1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="AL1" s="35" t="s">
+      <c r="AL1" s="31" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:42" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="96"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
-      <c r="D2" s="127"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="121"/>
-      <c r="G2" s="122"/>
-      <c r="H2" s="122"/>
-      <c r="I2" s="122"/>
-      <c r="J2" s="122"/>
-      <c r="K2" s="122"/>
-      <c r="L2" s="122"/>
-      <c r="M2" s="122"/>
-      <c r="N2" s="122"/>
-      <c r="O2" s="122"/>
-      <c r="P2" s="122"/>
-      <c r="Q2" s="122"/>
-      <c r="R2" s="122"/>
-      <c r="S2" s="122"/>
-      <c r="T2" s="122"/>
-      <c r="U2" s="122"/>
-      <c r="V2" s="122"/>
-      <c r="W2" s="122"/>
-      <c r="X2" s="122"/>
-      <c r="Y2" s="122"/>
-      <c r="Z2" s="122"/>
-      <c r="AA2" s="122"/>
-      <c r="AB2" s="122"/>
-      <c r="AC2" s="122"/>
-      <c r="AD2" s="122"/>
-      <c r="AE2" s="122"/>
-      <c r="AF2" s="122"/>
-      <c r="AG2" s="122"/>
-      <c r="AH2" s="122"/>
-      <c r="AI2" s="122"/>
-      <c r="AJ2" s="123"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
+      <c r="D2" s="126"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="120"/>
+      <c r="G2" s="121"/>
+      <c r="H2" s="121"/>
+      <c r="I2" s="121"/>
+      <c r="J2" s="121"/>
+      <c r="K2" s="121"/>
+      <c r="L2" s="121"/>
+      <c r="M2" s="121"/>
+      <c r="N2" s="121"/>
+      <c r="O2" s="121"/>
+      <c r="P2" s="121"/>
+      <c r="Q2" s="121"/>
+      <c r="R2" s="121"/>
+      <c r="S2" s="121"/>
+      <c r="T2" s="121"/>
+      <c r="U2" s="121"/>
+      <c r="V2" s="121"/>
+      <c r="W2" s="121"/>
+      <c r="X2" s="121"/>
+      <c r="Y2" s="121"/>
+      <c r="Z2" s="121"/>
+      <c r="AA2" s="121"/>
+      <c r="AB2" s="121"/>
+      <c r="AC2" s="121"/>
+      <c r="AD2" s="121"/>
+      <c r="AE2" s="121"/>
+      <c r="AF2" s="121"/>
+      <c r="AG2" s="121"/>
+      <c r="AH2" s="121"/>
+      <c r="AI2" s="121"/>
+      <c r="AJ2" s="122"/>
       <c r="AK2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="AL2" s="36">
+      <c r="AL2" s="32">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:42" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="96"/>
-      <c r="B3" s="96"/>
-      <c r="C3" s="96"/>
-      <c r="D3" s="127"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="121"/>
-      <c r="G3" s="122"/>
-      <c r="H3" s="122"/>
-      <c r="I3" s="122"/>
-      <c r="J3" s="122"/>
-      <c r="K3" s="122"/>
-      <c r="L3" s="122"/>
-      <c r="M3" s="122"/>
-      <c r="N3" s="122"/>
-      <c r="O3" s="122"/>
-      <c r="P3" s="122"/>
-      <c r="Q3" s="122"/>
-      <c r="R3" s="122"/>
-      <c r="S3" s="122"/>
-      <c r="T3" s="122"/>
-      <c r="U3" s="122"/>
-      <c r="V3" s="122"/>
-      <c r="W3" s="122"/>
-      <c r="X3" s="122"/>
-      <c r="Y3" s="122"/>
-      <c r="Z3" s="122"/>
-      <c r="AA3" s="122"/>
-      <c r="AB3" s="122"/>
-      <c r="AC3" s="122"/>
-      <c r="AD3" s="122"/>
-      <c r="AE3" s="122"/>
-      <c r="AF3" s="122"/>
-      <c r="AG3" s="122"/>
-      <c r="AH3" s="122"/>
-      <c r="AI3" s="122"/>
-      <c r="AJ3" s="123"/>
+      <c r="A3" s="95"/>
+      <c r="B3" s="95"/>
+      <c r="C3" s="95"/>
+      <c r="D3" s="126"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="120"/>
+      <c r="G3" s="121"/>
+      <c r="H3" s="121"/>
+      <c r="I3" s="121"/>
+      <c r="J3" s="121"/>
+      <c r="K3" s="121"/>
+      <c r="L3" s="121"/>
+      <c r="M3" s="121"/>
+      <c r="N3" s="121"/>
+      <c r="O3" s="121"/>
+      <c r="P3" s="121"/>
+      <c r="Q3" s="121"/>
+      <c r="R3" s="121"/>
+      <c r="S3" s="121"/>
+      <c r="T3" s="121"/>
+      <c r="U3" s="121"/>
+      <c r="V3" s="121"/>
+      <c r="W3" s="121"/>
+      <c r="X3" s="121"/>
+      <c r="Y3" s="121"/>
+      <c r="Z3" s="121"/>
+      <c r="AA3" s="121"/>
+      <c r="AB3" s="121"/>
+      <c r="AC3" s="121"/>
+      <c r="AD3" s="121"/>
+      <c r="AE3" s="121"/>
+      <c r="AF3" s="121"/>
+      <c r="AG3" s="121"/>
+      <c r="AH3" s="121"/>
+      <c r="AI3" s="121"/>
+      <c r="AJ3" s="122"/>
       <c r="AK3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="AL3" s="74">
+      <c r="AL3" s="69">
         <v>46072</v>
       </c>
       <c r="AP3" s="4" t="s">
@@ -3283,42 +3259,42 @@
       </c>
     </row>
     <row r="4" spans="1:42" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="96"/>
-      <c r="B4" s="96"/>
-      <c r="C4" s="96"/>
-      <c r="D4" s="127"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="124"/>
-      <c r="G4" s="125"/>
-      <c r="H4" s="125"/>
-      <c r="I4" s="125"/>
-      <c r="J4" s="125"/>
-      <c r="K4" s="125"/>
-      <c r="L4" s="125"/>
-      <c r="M4" s="125"/>
-      <c r="N4" s="125"/>
-      <c r="O4" s="125"/>
-      <c r="P4" s="125"/>
-      <c r="Q4" s="125"/>
-      <c r="R4" s="125"/>
-      <c r="S4" s="125"/>
-      <c r="T4" s="125"/>
-      <c r="U4" s="125"/>
-      <c r="V4" s="125"/>
-      <c r="W4" s="125"/>
-      <c r="X4" s="125"/>
-      <c r="Y4" s="125"/>
-      <c r="Z4" s="125"/>
-      <c r="AA4" s="125"/>
-      <c r="AB4" s="125"/>
-      <c r="AC4" s="125"/>
-      <c r="AD4" s="125"/>
-      <c r="AE4" s="125"/>
-      <c r="AF4" s="125"/>
-      <c r="AG4" s="125"/>
-      <c r="AH4" s="125"/>
-      <c r="AI4" s="125"/>
-      <c r="AJ4" s="126"/>
+      <c r="A4" s="95"/>
+      <c r="B4" s="95"/>
+      <c r="C4" s="95"/>
+      <c r="D4" s="126"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="123"/>
+      <c r="G4" s="124"/>
+      <c r="H4" s="124"/>
+      <c r="I4" s="124"/>
+      <c r="J4" s="124"/>
+      <c r="K4" s="124"/>
+      <c r="L4" s="124"/>
+      <c r="M4" s="124"/>
+      <c r="N4" s="124"/>
+      <c r="O4" s="124"/>
+      <c r="P4" s="124"/>
+      <c r="Q4" s="124"/>
+      <c r="R4" s="124"/>
+      <c r="S4" s="124"/>
+      <c r="T4" s="124"/>
+      <c r="U4" s="124"/>
+      <c r="V4" s="124"/>
+      <c r="W4" s="124"/>
+      <c r="X4" s="124"/>
+      <c r="Y4" s="124"/>
+      <c r="Z4" s="124"/>
+      <c r="AA4" s="124"/>
+      <c r="AB4" s="124"/>
+      <c r="AC4" s="124"/>
+      <c r="AD4" s="124"/>
+      <c r="AE4" s="124"/>
+      <c r="AF4" s="124"/>
+      <c r="AG4" s="124"/>
+      <c r="AH4" s="124"/>
+      <c r="AI4" s="124"/>
+      <c r="AJ4" s="125"/>
       <c r="AK4" s="1" t="s">
         <v>2</v>
       </c>
@@ -3370,120 +3346,120 @@
       <c r="AL5" s="7"/>
     </row>
     <row r="6" spans="1:42" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="114" t="s">
+      <c r="A6" s="113" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="114"/>
-      <c r="C6" s="114"/>
-      <c r="D6" s="115"/>
-      <c r="E6" s="50"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="48"/>
-      <c r="I6" s="42"/>
-      <c r="J6" s="42"/>
-      <c r="K6" s="42"/>
-      <c r="L6" s="42"/>
-      <c r="M6" s="53"/>
-      <c r="N6" s="46"/>
-      <c r="O6" s="45"/>
-      <c r="Q6" s="46"/>
-      <c r="R6" s="46"/>
-      <c r="S6" s="45"/>
-      <c r="U6" s="45"/>
-      <c r="W6" s="45"/>
-      <c r="Y6" s="45"/>
-      <c r="AA6" s="45"/>
-      <c r="AC6" s="45"/>
-      <c r="AE6" s="114"/>
-      <c r="AF6" s="114"/>
-      <c r="AG6" s="114"/>
-      <c r="AH6" s="114"/>
-      <c r="AI6" s="114" t="s">
+      <c r="B6" s="113"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="114"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="46"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="38"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="38"/>
+      <c r="L6" s="38"/>
+      <c r="M6" s="48"/>
+      <c r="N6" s="42"/>
+      <c r="O6" s="41"/>
+      <c r="Q6" s="42"/>
+      <c r="R6" s="42"/>
+      <c r="S6" s="41"/>
+      <c r="U6" s="41"/>
+      <c r="W6" s="41"/>
+      <c r="Y6" s="41"/>
+      <c r="AA6" s="41"/>
+      <c r="AC6" s="41"/>
+      <c r="AE6" s="113"/>
+      <c r="AF6" s="113"/>
+      <c r="AG6" s="113"/>
+      <c r="AH6" s="113"/>
+      <c r="AI6" s="113" t="s">
         <v>6</v>
       </c>
-      <c r="AJ6" s="115"/>
-      <c r="AK6" s="49"/>
-      <c r="AL6" s="69"/>
-    </row>
-    <row r="7" spans="1:42" s="43" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A7" s="40"/>
-      <c r="B7" s="41"/>
-      <c r="C7" s="42"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="42"/>
-      <c r="I7" s="42"/>
-      <c r="J7" s="42"/>
-      <c r="K7" s="42"/>
-      <c r="L7" s="42"/>
-      <c r="M7" s="45"/>
-      <c r="N7" s="45"/>
-      <c r="O7" s="46"/>
-      <c r="P7" s="46"/>
-      <c r="Q7" s="46"/>
-      <c r="R7" s="46"/>
-      <c r="S7" s="46"/>
-      <c r="T7" s="46"/>
-      <c r="U7" s="46"/>
-      <c r="V7" s="46"/>
-      <c r="W7" s="46"/>
-      <c r="X7" s="46"/>
-      <c r="Y7" s="46"/>
-      <c r="Z7" s="46"/>
-      <c r="AA7" s="46"/>
-      <c r="AB7" s="46"/>
-      <c r="AC7" s="46"/>
-      <c r="AD7" s="46"/>
-      <c r="AE7" s="46"/>
-      <c r="AF7" s="46"/>
-      <c r="AG7" s="46"/>
-      <c r="AH7" s="46"/>
-      <c r="AI7" s="46"/>
-      <c r="AJ7" s="46"/>
-      <c r="AK7" s="46"/>
-      <c r="AL7" s="46"/>
+      <c r="AJ6" s="114"/>
+      <c r="AK6" s="44"/>
+      <c r="AL6" s="64"/>
+    </row>
+    <row r="7" spans="1:42" s="39" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A7" s="36"/>
+      <c r="B7" s="37"/>
+      <c r="C7" s="38"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="38"/>
+      <c r="I7" s="38"/>
+      <c r="J7" s="38"/>
+      <c r="K7" s="38"/>
+      <c r="L7" s="38"/>
+      <c r="M7" s="41"/>
+      <c r="N7" s="41"/>
+      <c r="O7" s="42"/>
+      <c r="P7" s="42"/>
+      <c r="Q7" s="42"/>
+      <c r="R7" s="42"/>
+      <c r="S7" s="42"/>
+      <c r="T7" s="42"/>
+      <c r="U7" s="42"/>
+      <c r="V7" s="42"/>
+      <c r="W7" s="42"/>
+      <c r="X7" s="42"/>
+      <c r="Y7" s="42"/>
+      <c r="Z7" s="42"/>
+      <c r="AA7" s="42"/>
+      <c r="AB7" s="42"/>
+      <c r="AC7" s="42"/>
+      <c r="AD7" s="42"/>
+      <c r="AE7" s="42"/>
+      <c r="AF7" s="42"/>
+      <c r="AG7" s="42"/>
+      <c r="AH7" s="42"/>
+      <c r="AI7" s="42"/>
+      <c r="AJ7" s="42"/>
+      <c r="AK7" s="42"/>
+      <c r="AL7" s="42"/>
     </row>
     <row r="8" spans="1:42" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="116" t="s">
+      <c r="A8" s="115" t="s">
         <v>43</v>
       </c>
-      <c r="B8" s="116"/>
-      <c r="C8" s="116"/>
-      <c r="D8" s="116"/>
-      <c r="E8" s="117"/>
-      <c r="F8" s="129"/>
-      <c r="G8" s="130"/>
-      <c r="H8" s="130"/>
-      <c r="I8" s="130"/>
-      <c r="J8" s="130"/>
-      <c r="K8" s="130"/>
-      <c r="L8" s="130"/>
-      <c r="M8" s="130"/>
-      <c r="N8" s="130"/>
-      <c r="O8" s="130"/>
-      <c r="P8" s="130"/>
-      <c r="Q8" s="130"/>
-      <c r="R8" s="130"/>
-      <c r="S8" s="130"/>
-      <c r="T8" s="130"/>
-      <c r="U8" s="130"/>
-      <c r="V8" s="130"/>
-      <c r="W8" s="130"/>
-      <c r="X8" s="130"/>
-      <c r="Y8" s="130"/>
-      <c r="Z8" s="130"/>
-      <c r="AA8" s="130"/>
-      <c r="AB8" s="130"/>
-      <c r="AC8" s="130"/>
-      <c r="AD8" s="130"/>
-      <c r="AE8" s="130"/>
-      <c r="AF8" s="130"/>
-      <c r="AG8" s="130"/>
-      <c r="AH8" s="130"/>
-      <c r="AI8" s="130"/>
-      <c r="AJ8" s="130"/>
-      <c r="AK8" s="130"/>
-      <c r="AL8" s="131"/>
+      <c r="B8" s="115"/>
+      <c r="C8" s="115"/>
+      <c r="D8" s="115"/>
+      <c r="E8" s="116"/>
+      <c r="F8" s="127"/>
+      <c r="G8" s="128"/>
+      <c r="H8" s="128"/>
+      <c r="I8" s="128"/>
+      <c r="J8" s="128"/>
+      <c r="K8" s="128"/>
+      <c r="L8" s="128"/>
+      <c r="M8" s="128"/>
+      <c r="N8" s="128"/>
+      <c r="O8" s="128"/>
+      <c r="P8" s="128"/>
+      <c r="Q8" s="128"/>
+      <c r="R8" s="128"/>
+      <c r="S8" s="128"/>
+      <c r="T8" s="128"/>
+      <c r="U8" s="128"/>
+      <c r="V8" s="128"/>
+      <c r="W8" s="128"/>
+      <c r="X8" s="128"/>
+      <c r="Y8" s="128"/>
+      <c r="Z8" s="128"/>
+      <c r="AA8" s="128"/>
+      <c r="AB8" s="128"/>
+      <c r="AC8" s="128"/>
+      <c r="AD8" s="128"/>
+      <c r="AE8" s="128"/>
+      <c r="AF8" s="128"/>
+      <c r="AG8" s="128"/>
+      <c r="AH8" s="128"/>
+      <c r="AI8" s="128"/>
+      <c r="AJ8" s="128"/>
+      <c r="AK8" s="128"/>
+      <c r="AL8" s="129"/>
     </row>
     <row r="9" spans="1:42" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17"/>
@@ -3494,1378 +3470,1378 @@
       <c r="F9" s="3"/>
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
-      <c r="I9" s="52"/>
-      <c r="J9" s="52"/>
-      <c r="K9" s="52"/>
-      <c r="L9" s="52"/>
+      <c r="I9" s="47"/>
+      <c r="J9" s="47"/>
+      <c r="K9" s="47"/>
+      <c r="L9" s="47"/>
     </row>
     <row r="10" spans="1:42" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="135" t="s">
+      <c r="A10" s="130" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="135"/>
-      <c r="C10" s="136" t="s">
+      <c r="B10" s="130"/>
+      <c r="C10" s="131" t="s">
         <v>45</v>
       </c>
-      <c r="D10" s="136"/>
-      <c r="E10" s="136"/>
-      <c r="F10" s="136"/>
-      <c r="G10" s="136"/>
-      <c r="H10" s="136"/>
-      <c r="I10" s="136"/>
-      <c r="J10" s="136"/>
-      <c r="K10" s="136"/>
-      <c r="L10" s="136"/>
-      <c r="M10" s="136"/>
-      <c r="N10" s="136"/>
-      <c r="O10" s="136"/>
-      <c r="P10" s="136"/>
-      <c r="Q10" s="136"/>
-      <c r="R10" s="136"/>
-      <c r="S10" s="136"/>
-      <c r="T10" s="136"/>
-      <c r="U10" s="136"/>
-      <c r="V10" s="136"/>
-      <c r="W10" s="136"/>
-      <c r="X10" s="136"/>
-      <c r="Y10" s="136"/>
-      <c r="Z10" s="136"/>
-      <c r="AA10" s="136"/>
-      <c r="AB10" s="136"/>
-      <c r="AC10" s="136"/>
-      <c r="AD10" s="136"/>
-      <c r="AE10" s="136"/>
-      <c r="AF10" s="136"/>
-      <c r="AG10" s="136"/>
-      <c r="AH10" s="136"/>
-      <c r="AI10" s="136"/>
-      <c r="AJ10" s="136"/>
-      <c r="AK10" s="136"/>
-      <c r="AL10" s="136"/>
+      <c r="D10" s="131"/>
+      <c r="E10" s="131"/>
+      <c r="F10" s="131"/>
+      <c r="G10" s="131"/>
+      <c r="H10" s="131"/>
+      <c r="I10" s="131"/>
+      <c r="J10" s="131"/>
+      <c r="K10" s="131"/>
+      <c r="L10" s="131"/>
+      <c r="M10" s="131"/>
+      <c r="N10" s="131"/>
+      <c r="O10" s="131"/>
+      <c r="P10" s="131"/>
+      <c r="Q10" s="131"/>
+      <c r="R10" s="131"/>
+      <c r="S10" s="131"/>
+      <c r="T10" s="131"/>
+      <c r="U10" s="131"/>
+      <c r="V10" s="131"/>
+      <c r="W10" s="131"/>
+      <c r="X10" s="131"/>
+      <c r="Y10" s="131"/>
+      <c r="Z10" s="131"/>
+      <c r="AA10" s="131"/>
+      <c r="AB10" s="131"/>
+      <c r="AC10" s="131"/>
+      <c r="AD10" s="131"/>
+      <c r="AE10" s="131"/>
+      <c r="AF10" s="131"/>
+      <c r="AG10" s="131"/>
+      <c r="AH10" s="131"/>
+      <c r="AI10" s="131"/>
+      <c r="AJ10" s="131"/>
+      <c r="AK10" s="131"/>
+      <c r="AL10" s="131"/>
     </row>
     <row r="11" spans="1:42" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="135"/>
-      <c r="B11" s="135"/>
-      <c r="C11" s="128" t="s">
+      <c r="A11" s="130"/>
+      <c r="B11" s="130"/>
+      <c r="C11" s="132" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="128"/>
-      <c r="E11" s="78" t="s">
+      <c r="D11" s="132"/>
+      <c r="E11" s="73" t="s">
         <v>40</v>
       </c>
-      <c r="F11" s="78" t="s">
+      <c r="F11" s="73" t="s">
         <v>46</v>
       </c>
-      <c r="G11" s="79"/>
-      <c r="H11" s="80" t="s">
+      <c r="G11" s="133"/>
+      <c r="H11" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="I11" s="79"/>
-      <c r="J11" s="80" t="s">
+      <c r="I11" s="133"/>
+      <c r="J11" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="K11" s="79"/>
-      <c r="L11" s="80" t="s">
+      <c r="K11" s="133"/>
+      <c r="L11" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="M11" s="79"/>
-      <c r="N11" s="80" t="s">
+      <c r="M11" s="133"/>
+      <c r="N11" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="O11" s="79"/>
-      <c r="P11" s="80" t="s">
+      <c r="O11" s="133"/>
+      <c r="P11" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="Q11" s="79"/>
-      <c r="R11" s="80" t="s">
+      <c r="Q11" s="133"/>
+      <c r="R11" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="S11" s="79"/>
-      <c r="T11" s="80" t="s">
+      <c r="S11" s="133"/>
+      <c r="T11" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="U11" s="79"/>
-      <c r="V11" s="80" t="s">
+      <c r="U11" s="133"/>
+      <c r="V11" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="W11" s="79"/>
-      <c r="X11" s="80" t="s">
+      <c r="W11" s="133"/>
+      <c r="X11" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="Y11" s="79"/>
-      <c r="Z11" s="80" t="s">
+      <c r="Y11" s="133"/>
+      <c r="Z11" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="AA11" s="79"/>
-      <c r="AB11" s="80" t="s">
+      <c r="AA11" s="133"/>
+      <c r="AB11" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="AC11" s="79"/>
-      <c r="AD11" s="80" t="s">
+      <c r="AC11" s="133"/>
+      <c r="AD11" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="AE11" s="80"/>
-      <c r="AF11" s="80" t="s">
+      <c r="AE11" s="73"/>
+      <c r="AF11" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="AG11" s="80"/>
-      <c r="AH11" s="80" t="s">
+      <c r="AG11" s="73"/>
+      <c r="AH11" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="AI11" s="80"/>
-      <c r="AJ11" s="80" t="s">
+      <c r="AI11" s="73"/>
+      <c r="AJ11" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="AK11" s="79" t="s">
+      <c r="AK11" s="133" t="s">
         <v>47</v>
       </c>
-      <c r="AL11" s="79" t="s">
+      <c r="AL11" s="133" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:42" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="132"/>
-      <c r="B12" s="133"/>
-      <c r="C12" s="81"/>
-      <c r="D12" s="82"/>
-      <c r="E12" s="83"/>
-      <c r="F12" s="82"/>
-      <c r="G12" s="84"/>
-      <c r="H12" s="83"/>
-      <c r="I12" s="84"/>
-      <c r="J12" s="83"/>
-      <c r="K12" s="84"/>
-      <c r="L12" s="83"/>
-      <c r="M12" s="84"/>
-      <c r="N12" s="83"/>
-      <c r="O12" s="84"/>
-      <c r="P12" s="83"/>
-      <c r="Q12" s="84"/>
-      <c r="R12" s="83"/>
-      <c r="S12" s="84"/>
-      <c r="T12" s="83"/>
-      <c r="U12" s="84"/>
-      <c r="V12" s="83"/>
-      <c r="W12" s="84"/>
-      <c r="X12" s="83"/>
-      <c r="Y12" s="84"/>
-      <c r="Z12" s="83"/>
-      <c r="AA12" s="84"/>
-      <c r="AB12" s="83"/>
-      <c r="AC12" s="84"/>
-      <c r="AD12" s="83"/>
-      <c r="AE12" s="83"/>
-      <c r="AF12" s="83"/>
-      <c r="AG12" s="83"/>
-      <c r="AH12" s="83"/>
-      <c r="AI12" s="83"/>
-      <c r="AJ12" s="83"/>
-      <c r="AK12" s="83"/>
-      <c r="AL12" s="83"/>
+      <c r="A12" s="111"/>
+      <c r="B12" s="112"/>
+      <c r="C12" s="74"/>
+      <c r="D12" s="75"/>
+      <c r="E12" s="76"/>
+      <c r="F12" s="75"/>
+      <c r="G12" s="77"/>
+      <c r="H12" s="76"/>
+      <c r="I12" s="77"/>
+      <c r="J12" s="76"/>
+      <c r="K12" s="77"/>
+      <c r="L12" s="76"/>
+      <c r="M12" s="77"/>
+      <c r="N12" s="76"/>
+      <c r="O12" s="77"/>
+      <c r="P12" s="76"/>
+      <c r="Q12" s="77"/>
+      <c r="R12" s="76"/>
+      <c r="S12" s="77"/>
+      <c r="T12" s="76"/>
+      <c r="U12" s="77"/>
+      <c r="V12" s="76"/>
+      <c r="W12" s="77"/>
+      <c r="X12" s="76"/>
+      <c r="Y12" s="77"/>
+      <c r="Z12" s="76"/>
+      <c r="AA12" s="77"/>
+      <c r="AB12" s="76"/>
+      <c r="AC12" s="77"/>
+      <c r="AD12" s="76"/>
+      <c r="AE12" s="76"/>
+      <c r="AF12" s="76"/>
+      <c r="AG12" s="76"/>
+      <c r="AH12" s="76"/>
+      <c r="AI12" s="76"/>
+      <c r="AJ12" s="76"/>
+      <c r="AK12" s="76"/>
+      <c r="AL12" s="76"/>
     </row>
     <row r="13" spans="1:42" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="110"/>
-      <c r="B13" s="111"/>
-      <c r="C13" s="85"/>
-      <c r="D13" s="86"/>
-      <c r="E13" s="87"/>
-      <c r="F13" s="86"/>
-      <c r="G13" s="88"/>
-      <c r="H13" s="87"/>
-      <c r="I13" s="88"/>
-      <c r="J13" s="87"/>
-      <c r="K13" s="88"/>
-      <c r="L13" s="87"/>
-      <c r="M13" s="88"/>
-      <c r="N13" s="87"/>
-      <c r="O13" s="88"/>
-      <c r="P13" s="87"/>
-      <c r="Q13" s="88"/>
-      <c r="R13" s="87"/>
-      <c r="S13" s="88"/>
-      <c r="T13" s="87"/>
-      <c r="U13" s="88"/>
-      <c r="V13" s="87"/>
-      <c r="W13" s="88"/>
-      <c r="X13" s="87"/>
-      <c r="Y13" s="88"/>
-      <c r="Z13" s="87"/>
-      <c r="AA13" s="88"/>
-      <c r="AB13" s="87"/>
-      <c r="AC13" s="88"/>
-      <c r="AD13" s="87"/>
-      <c r="AE13" s="87"/>
-      <c r="AF13" s="87"/>
-      <c r="AG13" s="87"/>
-      <c r="AH13" s="87"/>
-      <c r="AI13" s="87"/>
-      <c r="AJ13" s="87"/>
-      <c r="AK13" s="87"/>
-      <c r="AL13" s="87"/>
+      <c r="A13" s="104"/>
+      <c r="B13" s="105"/>
+      <c r="C13" s="78"/>
+      <c r="D13" s="79"/>
+      <c r="E13" s="80"/>
+      <c r="F13" s="79"/>
+      <c r="G13" s="81"/>
+      <c r="H13" s="80"/>
+      <c r="I13" s="81"/>
+      <c r="J13" s="80"/>
+      <c r="K13" s="81"/>
+      <c r="L13" s="80"/>
+      <c r="M13" s="81"/>
+      <c r="N13" s="80"/>
+      <c r="O13" s="81"/>
+      <c r="P13" s="80"/>
+      <c r="Q13" s="81"/>
+      <c r="R13" s="80"/>
+      <c r="S13" s="81"/>
+      <c r="T13" s="80"/>
+      <c r="U13" s="81"/>
+      <c r="V13" s="80"/>
+      <c r="W13" s="81"/>
+      <c r="X13" s="80"/>
+      <c r="Y13" s="81"/>
+      <c r="Z13" s="80"/>
+      <c r="AA13" s="81"/>
+      <c r="AB13" s="80"/>
+      <c r="AC13" s="81"/>
+      <c r="AD13" s="80"/>
+      <c r="AE13" s="80"/>
+      <c r="AF13" s="80"/>
+      <c r="AG13" s="80"/>
+      <c r="AH13" s="80"/>
+      <c r="AI13" s="80"/>
+      <c r="AJ13" s="80"/>
+      <c r="AK13" s="80"/>
+      <c r="AL13" s="80"/>
     </row>
     <row r="14" spans="1:42" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="110"/>
-      <c r="B14" s="111"/>
-      <c r="C14" s="85"/>
-      <c r="D14" s="86"/>
-      <c r="E14" s="87"/>
-      <c r="F14" s="86"/>
-      <c r="G14" s="88"/>
-      <c r="H14" s="87"/>
-      <c r="I14" s="88"/>
-      <c r="J14" s="87"/>
-      <c r="K14" s="88"/>
-      <c r="L14" s="87"/>
-      <c r="M14" s="88"/>
-      <c r="N14" s="87"/>
-      <c r="O14" s="88"/>
-      <c r="P14" s="87"/>
-      <c r="Q14" s="88"/>
-      <c r="R14" s="87"/>
-      <c r="S14" s="88"/>
-      <c r="T14" s="87"/>
-      <c r="U14" s="88"/>
-      <c r="V14" s="87"/>
-      <c r="W14" s="88"/>
-      <c r="X14" s="87"/>
-      <c r="Y14" s="88"/>
-      <c r="Z14" s="87"/>
-      <c r="AA14" s="88"/>
-      <c r="AB14" s="87"/>
-      <c r="AC14" s="88"/>
-      <c r="AD14" s="87"/>
-      <c r="AE14" s="87"/>
-      <c r="AF14" s="87"/>
-      <c r="AG14" s="87"/>
-      <c r="AH14" s="87"/>
-      <c r="AI14" s="87"/>
-      <c r="AJ14" s="87"/>
-      <c r="AK14" s="87"/>
-      <c r="AL14" s="87"/>
+      <c r="A14" s="104"/>
+      <c r="B14" s="105"/>
+      <c r="C14" s="78"/>
+      <c r="D14" s="79"/>
+      <c r="E14" s="80"/>
+      <c r="F14" s="79"/>
+      <c r="G14" s="81"/>
+      <c r="H14" s="80"/>
+      <c r="I14" s="81"/>
+      <c r="J14" s="80"/>
+      <c r="K14" s="81"/>
+      <c r="L14" s="80"/>
+      <c r="M14" s="81"/>
+      <c r="N14" s="80"/>
+      <c r="O14" s="81"/>
+      <c r="P14" s="80"/>
+      <c r="Q14" s="81"/>
+      <c r="R14" s="80"/>
+      <c r="S14" s="81"/>
+      <c r="T14" s="80"/>
+      <c r="U14" s="81"/>
+      <c r="V14" s="80"/>
+      <c r="W14" s="81"/>
+      <c r="X14" s="80"/>
+      <c r="Y14" s="81"/>
+      <c r="Z14" s="80"/>
+      <c r="AA14" s="81"/>
+      <c r="AB14" s="80"/>
+      <c r="AC14" s="81"/>
+      <c r="AD14" s="80"/>
+      <c r="AE14" s="80"/>
+      <c r="AF14" s="80"/>
+      <c r="AG14" s="80"/>
+      <c r="AH14" s="80"/>
+      <c r="AI14" s="80"/>
+      <c r="AJ14" s="80"/>
+      <c r="AK14" s="80"/>
+      <c r="AL14" s="80"/>
     </row>
     <row r="15" spans="1:42" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="110"/>
-      <c r="B15" s="111"/>
-      <c r="C15" s="85"/>
-      <c r="D15" s="86"/>
-      <c r="E15" s="87"/>
-      <c r="F15" s="86"/>
-      <c r="G15" s="88"/>
-      <c r="H15" s="87"/>
-      <c r="I15" s="88"/>
-      <c r="J15" s="87"/>
-      <c r="K15" s="88"/>
-      <c r="L15" s="87"/>
-      <c r="M15" s="88"/>
-      <c r="N15" s="87"/>
-      <c r="O15" s="88"/>
-      <c r="P15" s="87"/>
-      <c r="Q15" s="88"/>
-      <c r="R15" s="87"/>
-      <c r="S15" s="88"/>
-      <c r="T15" s="87"/>
-      <c r="U15" s="88"/>
-      <c r="V15" s="87"/>
-      <c r="W15" s="88"/>
-      <c r="X15" s="87"/>
-      <c r="Y15" s="88"/>
-      <c r="Z15" s="87"/>
-      <c r="AA15" s="88"/>
-      <c r="AB15" s="87"/>
-      <c r="AC15" s="88"/>
-      <c r="AD15" s="87"/>
-      <c r="AE15" s="87"/>
-      <c r="AF15" s="87"/>
-      <c r="AG15" s="87"/>
-      <c r="AH15" s="87"/>
-      <c r="AI15" s="87"/>
-      <c r="AJ15" s="87"/>
-      <c r="AK15" s="87"/>
-      <c r="AL15" s="87"/>
+      <c r="A15" s="104"/>
+      <c r="B15" s="105"/>
+      <c r="C15" s="78"/>
+      <c r="D15" s="79"/>
+      <c r="E15" s="80"/>
+      <c r="F15" s="79"/>
+      <c r="G15" s="81"/>
+      <c r="H15" s="80"/>
+      <c r="I15" s="81"/>
+      <c r="J15" s="80"/>
+      <c r="K15" s="81"/>
+      <c r="L15" s="80"/>
+      <c r="M15" s="81"/>
+      <c r="N15" s="80"/>
+      <c r="O15" s="81"/>
+      <c r="P15" s="80"/>
+      <c r="Q15" s="81"/>
+      <c r="R15" s="80"/>
+      <c r="S15" s="81"/>
+      <c r="T15" s="80"/>
+      <c r="U15" s="81"/>
+      <c r="V15" s="80"/>
+      <c r="W15" s="81"/>
+      <c r="X15" s="80"/>
+      <c r="Y15" s="81"/>
+      <c r="Z15" s="80"/>
+      <c r="AA15" s="81"/>
+      <c r="AB15" s="80"/>
+      <c r="AC15" s="81"/>
+      <c r="AD15" s="80"/>
+      <c r="AE15" s="80"/>
+      <c r="AF15" s="80"/>
+      <c r="AG15" s="80"/>
+      <c r="AH15" s="80"/>
+      <c r="AI15" s="80"/>
+      <c r="AJ15" s="80"/>
+      <c r="AK15" s="80"/>
+      <c r="AL15" s="80"/>
     </row>
     <row r="16" spans="1:42" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="110"/>
-      <c r="B16" s="111"/>
-      <c r="C16" s="85"/>
-      <c r="D16" s="86"/>
-      <c r="E16" s="87"/>
-      <c r="F16" s="86"/>
-      <c r="G16" s="88"/>
-      <c r="H16" s="87"/>
-      <c r="I16" s="88"/>
-      <c r="J16" s="87"/>
-      <c r="K16" s="88"/>
-      <c r="L16" s="87"/>
-      <c r="M16" s="88"/>
-      <c r="N16" s="87"/>
-      <c r="O16" s="88"/>
-      <c r="P16" s="87"/>
-      <c r="Q16" s="88"/>
-      <c r="R16" s="87"/>
-      <c r="S16" s="88"/>
-      <c r="T16" s="87"/>
-      <c r="U16" s="88"/>
-      <c r="V16" s="87"/>
-      <c r="W16" s="88"/>
-      <c r="X16" s="87"/>
-      <c r="Y16" s="88"/>
-      <c r="Z16" s="87"/>
-      <c r="AA16" s="88"/>
-      <c r="AB16" s="87"/>
-      <c r="AC16" s="88"/>
-      <c r="AD16" s="87"/>
-      <c r="AE16" s="87"/>
-      <c r="AF16" s="87"/>
-      <c r="AG16" s="87"/>
-      <c r="AH16" s="87"/>
-      <c r="AI16" s="87"/>
-      <c r="AJ16" s="87"/>
-      <c r="AK16" s="87"/>
-      <c r="AL16" s="87"/>
+      <c r="A16" s="104"/>
+      <c r="B16" s="105"/>
+      <c r="C16" s="78"/>
+      <c r="D16" s="79"/>
+      <c r="E16" s="80"/>
+      <c r="F16" s="79"/>
+      <c r="G16" s="81"/>
+      <c r="H16" s="80"/>
+      <c r="I16" s="81"/>
+      <c r="J16" s="80"/>
+      <c r="K16" s="81"/>
+      <c r="L16" s="80"/>
+      <c r="M16" s="81"/>
+      <c r="N16" s="80"/>
+      <c r="O16" s="81"/>
+      <c r="P16" s="80"/>
+      <c r="Q16" s="81"/>
+      <c r="R16" s="80"/>
+      <c r="S16" s="81"/>
+      <c r="T16" s="80"/>
+      <c r="U16" s="81"/>
+      <c r="V16" s="80"/>
+      <c r="W16" s="81"/>
+      <c r="X16" s="80"/>
+      <c r="Y16" s="81"/>
+      <c r="Z16" s="80"/>
+      <c r="AA16" s="81"/>
+      <c r="AB16" s="80"/>
+      <c r="AC16" s="81"/>
+      <c r="AD16" s="80"/>
+      <c r="AE16" s="80"/>
+      <c r="AF16" s="80"/>
+      <c r="AG16" s="80"/>
+      <c r="AH16" s="80"/>
+      <c r="AI16" s="80"/>
+      <c r="AJ16" s="80"/>
+      <c r="AK16" s="80"/>
+      <c r="AL16" s="80"/>
     </row>
     <row r="17" spans="1:38" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="110"/>
-      <c r="B17" s="111"/>
-      <c r="C17" s="85"/>
-      <c r="D17" s="86"/>
-      <c r="E17" s="87"/>
-      <c r="F17" s="86"/>
-      <c r="G17" s="88"/>
-      <c r="H17" s="87"/>
-      <c r="I17" s="88"/>
-      <c r="J17" s="87"/>
-      <c r="K17" s="88"/>
-      <c r="L17" s="87"/>
-      <c r="M17" s="88"/>
-      <c r="N17" s="87"/>
-      <c r="O17" s="88"/>
-      <c r="P17" s="87"/>
-      <c r="Q17" s="88"/>
-      <c r="R17" s="87"/>
-      <c r="S17" s="88"/>
-      <c r="T17" s="87"/>
-      <c r="U17" s="88"/>
-      <c r="V17" s="87"/>
-      <c r="W17" s="88"/>
-      <c r="X17" s="87"/>
-      <c r="Y17" s="88"/>
-      <c r="Z17" s="87"/>
-      <c r="AA17" s="88"/>
-      <c r="AB17" s="87"/>
-      <c r="AC17" s="88"/>
-      <c r="AD17" s="87"/>
-      <c r="AE17" s="87"/>
-      <c r="AF17" s="87"/>
-      <c r="AG17" s="87"/>
-      <c r="AH17" s="87"/>
-      <c r="AI17" s="87"/>
-      <c r="AJ17" s="87"/>
-      <c r="AK17" s="87"/>
-      <c r="AL17" s="87"/>
+      <c r="A17" s="104"/>
+      <c r="B17" s="105"/>
+      <c r="C17" s="78"/>
+      <c r="D17" s="79"/>
+      <c r="E17" s="80"/>
+      <c r="F17" s="79"/>
+      <c r="G17" s="81"/>
+      <c r="H17" s="80"/>
+      <c r="I17" s="81"/>
+      <c r="J17" s="80"/>
+      <c r="K17" s="81"/>
+      <c r="L17" s="80"/>
+      <c r="M17" s="81"/>
+      <c r="N17" s="80"/>
+      <c r="O17" s="81"/>
+      <c r="P17" s="80"/>
+      <c r="Q17" s="81"/>
+      <c r="R17" s="80"/>
+      <c r="S17" s="81"/>
+      <c r="T17" s="80"/>
+      <c r="U17" s="81"/>
+      <c r="V17" s="80"/>
+      <c r="W17" s="81"/>
+      <c r="X17" s="80"/>
+      <c r="Y17" s="81"/>
+      <c r="Z17" s="80"/>
+      <c r="AA17" s="81"/>
+      <c r="AB17" s="80"/>
+      <c r="AC17" s="81"/>
+      <c r="AD17" s="80"/>
+      <c r="AE17" s="80"/>
+      <c r="AF17" s="80"/>
+      <c r="AG17" s="80"/>
+      <c r="AH17" s="80"/>
+      <c r="AI17" s="80"/>
+      <c r="AJ17" s="80"/>
+      <c r="AK17" s="80"/>
+      <c r="AL17" s="80"/>
     </row>
     <row r="18" spans="1:38" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="110"/>
-      <c r="B18" s="111"/>
-      <c r="C18" s="112"/>
-      <c r="D18" s="113"/>
-      <c r="E18" s="87"/>
-      <c r="F18" s="86"/>
-      <c r="G18" s="88"/>
-      <c r="H18" s="87"/>
-      <c r="I18" s="88"/>
-      <c r="J18" s="87"/>
-      <c r="K18" s="88"/>
-      <c r="L18" s="87"/>
-      <c r="M18" s="88"/>
-      <c r="N18" s="87"/>
-      <c r="O18" s="88"/>
-      <c r="P18" s="87"/>
-      <c r="Q18" s="88"/>
-      <c r="R18" s="87"/>
-      <c r="S18" s="88"/>
-      <c r="T18" s="87"/>
-      <c r="U18" s="88"/>
-      <c r="V18" s="87"/>
-      <c r="W18" s="88"/>
-      <c r="X18" s="87"/>
-      <c r="Y18" s="88"/>
-      <c r="Z18" s="87"/>
-      <c r="AA18" s="88"/>
-      <c r="AB18" s="87"/>
-      <c r="AC18" s="88"/>
-      <c r="AD18" s="87"/>
-      <c r="AE18" s="87"/>
-      <c r="AF18" s="87"/>
-      <c r="AG18" s="87"/>
-      <c r="AH18" s="87"/>
-      <c r="AI18" s="87"/>
-      <c r="AJ18" s="87"/>
-      <c r="AK18" s="87"/>
-      <c r="AL18" s="87"/>
+      <c r="A18" s="104"/>
+      <c r="B18" s="105"/>
+      <c r="C18" s="109"/>
+      <c r="D18" s="110"/>
+      <c r="E18" s="80"/>
+      <c r="F18" s="79"/>
+      <c r="G18" s="81"/>
+      <c r="H18" s="80"/>
+      <c r="I18" s="81"/>
+      <c r="J18" s="80"/>
+      <c r="K18" s="81"/>
+      <c r="L18" s="80"/>
+      <c r="M18" s="81"/>
+      <c r="N18" s="80"/>
+      <c r="O18" s="81"/>
+      <c r="P18" s="80"/>
+      <c r="Q18" s="81"/>
+      <c r="R18" s="80"/>
+      <c r="S18" s="81"/>
+      <c r="T18" s="80"/>
+      <c r="U18" s="81"/>
+      <c r="V18" s="80"/>
+      <c r="W18" s="81"/>
+      <c r="X18" s="80"/>
+      <c r="Y18" s="81"/>
+      <c r="Z18" s="80"/>
+      <c r="AA18" s="81"/>
+      <c r="AB18" s="80"/>
+      <c r="AC18" s="81"/>
+      <c r="AD18" s="80"/>
+      <c r="AE18" s="80"/>
+      <c r="AF18" s="80"/>
+      <c r="AG18" s="80"/>
+      <c r="AH18" s="80"/>
+      <c r="AI18" s="80"/>
+      <c r="AJ18" s="80"/>
+      <c r="AK18" s="80"/>
+      <c r="AL18" s="80"/>
     </row>
     <row r="19" spans="1:38" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="110"/>
-      <c r="B19" s="111"/>
-      <c r="C19" s="112"/>
-      <c r="D19" s="113"/>
-      <c r="E19" s="87"/>
-      <c r="F19" s="86"/>
-      <c r="G19" s="88"/>
-      <c r="H19" s="87"/>
-      <c r="I19" s="88"/>
-      <c r="J19" s="87"/>
-      <c r="K19" s="88"/>
-      <c r="L19" s="87"/>
-      <c r="M19" s="88"/>
-      <c r="N19" s="87"/>
-      <c r="O19" s="88"/>
-      <c r="P19" s="87"/>
-      <c r="Q19" s="88"/>
-      <c r="R19" s="87"/>
-      <c r="S19" s="88"/>
-      <c r="T19" s="87"/>
-      <c r="U19" s="88"/>
-      <c r="V19" s="87"/>
-      <c r="W19" s="88"/>
-      <c r="X19" s="87"/>
-      <c r="Y19" s="88"/>
-      <c r="Z19" s="87"/>
-      <c r="AA19" s="88"/>
-      <c r="AB19" s="87"/>
-      <c r="AC19" s="88"/>
-      <c r="AD19" s="87"/>
-      <c r="AE19" s="87"/>
-      <c r="AF19" s="87"/>
-      <c r="AG19" s="87"/>
-      <c r="AH19" s="87"/>
-      <c r="AI19" s="87"/>
-      <c r="AJ19" s="87"/>
-      <c r="AK19" s="87"/>
-      <c r="AL19" s="87"/>
+      <c r="A19" s="104"/>
+      <c r="B19" s="105"/>
+      <c r="C19" s="109"/>
+      <c r="D19" s="110"/>
+      <c r="E19" s="80"/>
+      <c r="F19" s="79"/>
+      <c r="G19" s="81"/>
+      <c r="H19" s="80"/>
+      <c r="I19" s="81"/>
+      <c r="J19" s="80"/>
+      <c r="K19" s="81"/>
+      <c r="L19" s="80"/>
+      <c r="M19" s="81"/>
+      <c r="N19" s="80"/>
+      <c r="O19" s="81"/>
+      <c r="P19" s="80"/>
+      <c r="Q19" s="81"/>
+      <c r="R19" s="80"/>
+      <c r="S19" s="81"/>
+      <c r="T19" s="80"/>
+      <c r="U19" s="81"/>
+      <c r="V19" s="80"/>
+      <c r="W19" s="81"/>
+      <c r="X19" s="80"/>
+      <c r="Y19" s="81"/>
+      <c r="Z19" s="80"/>
+      <c r="AA19" s="81"/>
+      <c r="AB19" s="80"/>
+      <c r="AC19" s="81"/>
+      <c r="AD19" s="80"/>
+      <c r="AE19" s="80"/>
+      <c r="AF19" s="80"/>
+      <c r="AG19" s="80"/>
+      <c r="AH19" s="80"/>
+      <c r="AI19" s="80"/>
+      <c r="AJ19" s="80"/>
+      <c r="AK19" s="80"/>
+      <c r="AL19" s="80"/>
     </row>
     <row r="20" spans="1:38" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="110"/>
-      <c r="B20" s="111"/>
-      <c r="C20" s="112"/>
-      <c r="D20" s="113"/>
-      <c r="E20" s="87"/>
-      <c r="F20" s="86"/>
-      <c r="G20" s="88"/>
-      <c r="H20" s="87"/>
-      <c r="I20" s="88"/>
-      <c r="J20" s="87"/>
-      <c r="K20" s="88"/>
-      <c r="L20" s="87"/>
-      <c r="M20" s="88"/>
-      <c r="N20" s="87"/>
-      <c r="O20" s="88"/>
-      <c r="P20" s="87"/>
-      <c r="Q20" s="88"/>
-      <c r="R20" s="87"/>
-      <c r="S20" s="88"/>
-      <c r="T20" s="87"/>
-      <c r="U20" s="88"/>
-      <c r="V20" s="87"/>
-      <c r="W20" s="88"/>
-      <c r="X20" s="87"/>
-      <c r="Y20" s="88"/>
-      <c r="Z20" s="87"/>
-      <c r="AA20" s="88"/>
-      <c r="AB20" s="87"/>
-      <c r="AC20" s="88"/>
-      <c r="AD20" s="87"/>
-      <c r="AE20" s="87"/>
-      <c r="AF20" s="87"/>
-      <c r="AG20" s="87"/>
-      <c r="AH20" s="87"/>
-      <c r="AI20" s="87"/>
-      <c r="AJ20" s="87"/>
-      <c r="AK20" s="87"/>
-      <c r="AL20" s="87"/>
+      <c r="A20" s="104"/>
+      <c r="B20" s="105"/>
+      <c r="C20" s="109"/>
+      <c r="D20" s="110"/>
+      <c r="E20" s="80"/>
+      <c r="F20" s="79"/>
+      <c r="G20" s="81"/>
+      <c r="H20" s="80"/>
+      <c r="I20" s="81"/>
+      <c r="J20" s="80"/>
+      <c r="K20" s="81"/>
+      <c r="L20" s="80"/>
+      <c r="M20" s="81"/>
+      <c r="N20" s="80"/>
+      <c r="O20" s="81"/>
+      <c r="P20" s="80"/>
+      <c r="Q20" s="81"/>
+      <c r="R20" s="80"/>
+      <c r="S20" s="81"/>
+      <c r="T20" s="80"/>
+      <c r="U20" s="81"/>
+      <c r="V20" s="80"/>
+      <c r="W20" s="81"/>
+      <c r="X20" s="80"/>
+      <c r="Y20" s="81"/>
+      <c r="Z20" s="80"/>
+      <c r="AA20" s="81"/>
+      <c r="AB20" s="80"/>
+      <c r="AC20" s="81"/>
+      <c r="AD20" s="80"/>
+      <c r="AE20" s="80"/>
+      <c r="AF20" s="80"/>
+      <c r="AG20" s="80"/>
+      <c r="AH20" s="80"/>
+      <c r="AI20" s="80"/>
+      <c r="AJ20" s="80"/>
+      <c r="AK20" s="80"/>
+      <c r="AL20" s="80"/>
     </row>
     <row r="21" spans="1:38" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="110"/>
-      <c r="B21" s="111"/>
-      <c r="C21" s="112"/>
-      <c r="D21" s="113"/>
-      <c r="E21" s="89"/>
-      <c r="F21" s="86"/>
-      <c r="G21" s="89"/>
-      <c r="H21" s="89"/>
-      <c r="I21" s="89"/>
-      <c r="J21" s="89"/>
-      <c r="K21" s="89"/>
-      <c r="L21" s="89"/>
-      <c r="M21" s="89"/>
-      <c r="N21" s="89"/>
-      <c r="O21" s="89"/>
-      <c r="P21" s="89"/>
-      <c r="Q21" s="89"/>
-      <c r="R21" s="89"/>
-      <c r="S21" s="89"/>
-      <c r="T21" s="89"/>
-      <c r="U21" s="89"/>
-      <c r="V21" s="89"/>
-      <c r="W21" s="89"/>
-      <c r="X21" s="89"/>
-      <c r="Y21" s="89"/>
-      <c r="Z21" s="89"/>
-      <c r="AA21" s="89"/>
-      <c r="AB21" s="89"/>
-      <c r="AC21" s="89"/>
-      <c r="AD21" s="89"/>
-      <c r="AE21" s="89"/>
-      <c r="AF21" s="89"/>
-      <c r="AG21" s="89"/>
-      <c r="AH21" s="89"/>
-      <c r="AI21" s="89"/>
-      <c r="AJ21" s="89"/>
-      <c r="AK21" s="89"/>
-      <c r="AL21" s="89"/>
+      <c r="A21" s="104"/>
+      <c r="B21" s="105"/>
+      <c r="C21" s="109"/>
+      <c r="D21" s="110"/>
+      <c r="E21" s="82"/>
+      <c r="F21" s="79"/>
+      <c r="G21" s="82"/>
+      <c r="H21" s="82"/>
+      <c r="I21" s="82"/>
+      <c r="J21" s="82"/>
+      <c r="K21" s="82"/>
+      <c r="L21" s="82"/>
+      <c r="M21" s="82"/>
+      <c r="N21" s="82"/>
+      <c r="O21" s="82"/>
+      <c r="P21" s="82"/>
+      <c r="Q21" s="82"/>
+      <c r="R21" s="82"/>
+      <c r="S21" s="82"/>
+      <c r="T21" s="82"/>
+      <c r="U21" s="82"/>
+      <c r="V21" s="82"/>
+      <c r="W21" s="82"/>
+      <c r="X21" s="82"/>
+      <c r="Y21" s="82"/>
+      <c r="Z21" s="82"/>
+      <c r="AA21" s="82"/>
+      <c r="AB21" s="82"/>
+      <c r="AC21" s="82"/>
+      <c r="AD21" s="82"/>
+      <c r="AE21" s="82"/>
+      <c r="AF21" s="82"/>
+      <c r="AG21" s="82"/>
+      <c r="AH21" s="82"/>
+      <c r="AI21" s="82"/>
+      <c r="AJ21" s="82"/>
+      <c r="AK21" s="82"/>
+      <c r="AL21" s="82"/>
     </row>
     <row r="22" spans="1:38" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="110"/>
-      <c r="B22" s="111"/>
-      <c r="C22" s="112"/>
-      <c r="D22" s="113"/>
-      <c r="E22" s="87"/>
-      <c r="F22" s="86"/>
-      <c r="G22" s="88"/>
-      <c r="H22" s="87"/>
-      <c r="I22" s="88"/>
-      <c r="J22" s="87"/>
-      <c r="K22" s="88"/>
-      <c r="L22" s="87"/>
-      <c r="M22" s="88"/>
-      <c r="N22" s="87"/>
-      <c r="O22" s="88"/>
-      <c r="P22" s="87"/>
-      <c r="Q22" s="88"/>
-      <c r="R22" s="87"/>
-      <c r="S22" s="88"/>
-      <c r="T22" s="87"/>
-      <c r="U22" s="88"/>
-      <c r="V22" s="87"/>
-      <c r="W22" s="88"/>
-      <c r="X22" s="87"/>
-      <c r="Y22" s="88"/>
-      <c r="Z22" s="87"/>
-      <c r="AA22" s="88"/>
-      <c r="AB22" s="87"/>
-      <c r="AC22" s="88"/>
-      <c r="AD22" s="87"/>
-      <c r="AE22" s="87"/>
-      <c r="AF22" s="87"/>
-      <c r="AG22" s="87"/>
-      <c r="AH22" s="87"/>
-      <c r="AI22" s="87"/>
-      <c r="AJ22" s="87"/>
-      <c r="AK22" s="87"/>
-      <c r="AL22" s="87"/>
+      <c r="A22" s="104"/>
+      <c r="B22" s="105"/>
+      <c r="C22" s="109"/>
+      <c r="D22" s="110"/>
+      <c r="E22" s="80"/>
+      <c r="F22" s="79"/>
+      <c r="G22" s="81"/>
+      <c r="H22" s="80"/>
+      <c r="I22" s="81"/>
+      <c r="J22" s="80"/>
+      <c r="K22" s="81"/>
+      <c r="L22" s="80"/>
+      <c r="M22" s="81"/>
+      <c r="N22" s="80"/>
+      <c r="O22" s="81"/>
+      <c r="P22" s="80"/>
+      <c r="Q22" s="81"/>
+      <c r="R22" s="80"/>
+      <c r="S22" s="81"/>
+      <c r="T22" s="80"/>
+      <c r="U22" s="81"/>
+      <c r="V22" s="80"/>
+      <c r="W22" s="81"/>
+      <c r="X22" s="80"/>
+      <c r="Y22" s="81"/>
+      <c r="Z22" s="80"/>
+      <c r="AA22" s="81"/>
+      <c r="AB22" s="80"/>
+      <c r="AC22" s="81"/>
+      <c r="AD22" s="80"/>
+      <c r="AE22" s="80"/>
+      <c r="AF22" s="80"/>
+      <c r="AG22" s="80"/>
+      <c r="AH22" s="80"/>
+      <c r="AI22" s="80"/>
+      <c r="AJ22" s="80"/>
+      <c r="AK22" s="80"/>
+      <c r="AL22" s="80"/>
     </row>
     <row r="23" spans="1:38" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="110"/>
-      <c r="B23" s="111"/>
-      <c r="C23" s="112"/>
-      <c r="D23" s="113"/>
-      <c r="E23" s="87"/>
-      <c r="F23" s="86"/>
-      <c r="G23" s="88"/>
-      <c r="H23" s="87"/>
-      <c r="I23" s="88"/>
-      <c r="J23" s="87"/>
-      <c r="K23" s="88"/>
-      <c r="L23" s="87"/>
-      <c r="M23" s="88"/>
-      <c r="N23" s="87"/>
-      <c r="O23" s="88"/>
-      <c r="P23" s="87"/>
-      <c r="Q23" s="88"/>
-      <c r="R23" s="87"/>
-      <c r="S23" s="88"/>
-      <c r="T23" s="87"/>
-      <c r="U23" s="88"/>
-      <c r="V23" s="87"/>
-      <c r="W23" s="88"/>
-      <c r="X23" s="87"/>
-      <c r="Y23" s="88"/>
-      <c r="Z23" s="87"/>
-      <c r="AA23" s="88"/>
-      <c r="AB23" s="87"/>
-      <c r="AC23" s="88"/>
-      <c r="AD23" s="87"/>
-      <c r="AE23" s="87"/>
-      <c r="AF23" s="87"/>
-      <c r="AG23" s="87"/>
-      <c r="AH23" s="87"/>
-      <c r="AI23" s="87"/>
-      <c r="AJ23" s="87"/>
-      <c r="AK23" s="87"/>
-      <c r="AL23" s="87"/>
+      <c r="A23" s="104"/>
+      <c r="B23" s="105"/>
+      <c r="C23" s="109"/>
+      <c r="D23" s="110"/>
+      <c r="E23" s="80"/>
+      <c r="F23" s="79"/>
+      <c r="G23" s="81"/>
+      <c r="H23" s="80"/>
+      <c r="I23" s="81"/>
+      <c r="J23" s="80"/>
+      <c r="K23" s="81"/>
+      <c r="L23" s="80"/>
+      <c r="M23" s="81"/>
+      <c r="N23" s="80"/>
+      <c r="O23" s="81"/>
+      <c r="P23" s="80"/>
+      <c r="Q23" s="81"/>
+      <c r="R23" s="80"/>
+      <c r="S23" s="81"/>
+      <c r="T23" s="80"/>
+      <c r="U23" s="81"/>
+      <c r="V23" s="80"/>
+      <c r="W23" s="81"/>
+      <c r="X23" s="80"/>
+      <c r="Y23" s="81"/>
+      <c r="Z23" s="80"/>
+      <c r="AA23" s="81"/>
+      <c r="AB23" s="80"/>
+      <c r="AC23" s="81"/>
+      <c r="AD23" s="80"/>
+      <c r="AE23" s="80"/>
+      <c r="AF23" s="80"/>
+      <c r="AG23" s="80"/>
+      <c r="AH23" s="80"/>
+      <c r="AI23" s="80"/>
+      <c r="AJ23" s="80"/>
+      <c r="AK23" s="80"/>
+      <c r="AL23" s="80"/>
     </row>
     <row r="24" spans="1:38" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="110"/>
-      <c r="B24" s="111"/>
-      <c r="C24" s="112"/>
-      <c r="D24" s="113"/>
-      <c r="E24" s="89"/>
-      <c r="F24" s="86"/>
-      <c r="G24" s="89"/>
-      <c r="H24" s="89"/>
-      <c r="I24" s="89"/>
-      <c r="J24" s="89"/>
-      <c r="K24" s="89"/>
-      <c r="L24" s="89"/>
-      <c r="M24" s="89"/>
-      <c r="N24" s="89"/>
-      <c r="O24" s="89"/>
-      <c r="P24" s="89"/>
-      <c r="Q24" s="89"/>
-      <c r="R24" s="89"/>
-      <c r="S24" s="89"/>
-      <c r="T24" s="89"/>
-      <c r="U24" s="89"/>
-      <c r="V24" s="89"/>
-      <c r="W24" s="89"/>
-      <c r="X24" s="89"/>
-      <c r="Y24" s="89"/>
-      <c r="Z24" s="89"/>
-      <c r="AA24" s="89"/>
-      <c r="AB24" s="89"/>
-      <c r="AC24" s="89"/>
-      <c r="AD24" s="89"/>
-      <c r="AE24" s="89"/>
-      <c r="AF24" s="89"/>
-      <c r="AG24" s="89"/>
-      <c r="AH24" s="89"/>
-      <c r="AI24" s="89"/>
-      <c r="AJ24" s="89"/>
-      <c r="AK24" s="89"/>
-      <c r="AL24" s="89"/>
+      <c r="A24" s="104"/>
+      <c r="B24" s="105"/>
+      <c r="C24" s="109"/>
+      <c r="D24" s="110"/>
+      <c r="E24" s="82"/>
+      <c r="F24" s="79"/>
+      <c r="G24" s="82"/>
+      <c r="H24" s="82"/>
+      <c r="I24" s="82"/>
+      <c r="J24" s="82"/>
+      <c r="K24" s="82"/>
+      <c r="L24" s="82"/>
+      <c r="M24" s="82"/>
+      <c r="N24" s="82"/>
+      <c r="O24" s="82"/>
+      <c r="P24" s="82"/>
+      <c r="Q24" s="82"/>
+      <c r="R24" s="82"/>
+      <c r="S24" s="82"/>
+      <c r="T24" s="82"/>
+      <c r="U24" s="82"/>
+      <c r="V24" s="82"/>
+      <c r="W24" s="82"/>
+      <c r="X24" s="82"/>
+      <c r="Y24" s="82"/>
+      <c r="Z24" s="82"/>
+      <c r="AA24" s="82"/>
+      <c r="AB24" s="82"/>
+      <c r="AC24" s="82"/>
+      <c r="AD24" s="82"/>
+      <c r="AE24" s="82"/>
+      <c r="AF24" s="82"/>
+      <c r="AG24" s="82"/>
+      <c r="AH24" s="82"/>
+      <c r="AI24" s="82"/>
+      <c r="AJ24" s="82"/>
+      <c r="AK24" s="82"/>
+      <c r="AL24" s="82"/>
     </row>
     <row r="25" spans="1:38" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="110"/>
-      <c r="B25" s="111"/>
-      <c r="C25" s="112"/>
-      <c r="D25" s="113"/>
-      <c r="E25" s="87"/>
-      <c r="F25" s="86"/>
-      <c r="G25" s="88"/>
-      <c r="H25" s="87"/>
-      <c r="I25" s="88"/>
-      <c r="J25" s="87"/>
-      <c r="K25" s="88"/>
-      <c r="L25" s="87"/>
-      <c r="M25" s="88"/>
-      <c r="N25" s="87"/>
-      <c r="O25" s="88"/>
-      <c r="P25" s="87"/>
-      <c r="Q25" s="88"/>
-      <c r="R25" s="87"/>
-      <c r="S25" s="88"/>
-      <c r="T25" s="87"/>
-      <c r="U25" s="88"/>
-      <c r="V25" s="87"/>
-      <c r="W25" s="88"/>
-      <c r="X25" s="87"/>
-      <c r="Y25" s="88"/>
-      <c r="Z25" s="87"/>
-      <c r="AA25" s="88"/>
-      <c r="AB25" s="87"/>
-      <c r="AC25" s="88"/>
-      <c r="AD25" s="87"/>
-      <c r="AE25" s="87"/>
-      <c r="AF25" s="87"/>
-      <c r="AG25" s="87"/>
-      <c r="AH25" s="87"/>
-      <c r="AI25" s="87"/>
-      <c r="AJ25" s="87"/>
-      <c r="AK25" s="87"/>
-      <c r="AL25" s="87"/>
+      <c r="A25" s="104"/>
+      <c r="B25" s="105"/>
+      <c r="C25" s="109"/>
+      <c r="D25" s="110"/>
+      <c r="E25" s="80"/>
+      <c r="F25" s="79"/>
+      <c r="G25" s="81"/>
+      <c r="H25" s="80"/>
+      <c r="I25" s="81"/>
+      <c r="J25" s="80"/>
+      <c r="K25" s="81"/>
+      <c r="L25" s="80"/>
+      <c r="M25" s="81"/>
+      <c r="N25" s="80"/>
+      <c r="O25" s="81"/>
+      <c r="P25" s="80"/>
+      <c r="Q25" s="81"/>
+      <c r="R25" s="80"/>
+      <c r="S25" s="81"/>
+      <c r="T25" s="80"/>
+      <c r="U25" s="81"/>
+      <c r="V25" s="80"/>
+      <c r="W25" s="81"/>
+      <c r="X25" s="80"/>
+      <c r="Y25" s="81"/>
+      <c r="Z25" s="80"/>
+      <c r="AA25" s="81"/>
+      <c r="AB25" s="80"/>
+      <c r="AC25" s="81"/>
+      <c r="AD25" s="80"/>
+      <c r="AE25" s="80"/>
+      <c r="AF25" s="80"/>
+      <c r="AG25" s="80"/>
+      <c r="AH25" s="80"/>
+      <c r="AI25" s="80"/>
+      <c r="AJ25" s="80"/>
+      <c r="AK25" s="80"/>
+      <c r="AL25" s="80"/>
     </row>
     <row r="26" spans="1:38" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="110"/>
-      <c r="B26" s="111"/>
-      <c r="C26" s="112"/>
-      <c r="D26" s="113"/>
-      <c r="E26" s="89"/>
-      <c r="F26" s="86"/>
-      <c r="G26" s="89"/>
-      <c r="H26" s="89"/>
-      <c r="I26" s="89"/>
-      <c r="J26" s="89"/>
-      <c r="K26" s="89"/>
-      <c r="L26" s="89"/>
-      <c r="M26" s="89"/>
-      <c r="N26" s="89"/>
-      <c r="O26" s="89"/>
-      <c r="P26" s="89"/>
-      <c r="Q26" s="89"/>
-      <c r="R26" s="89"/>
-      <c r="S26" s="89"/>
-      <c r="T26" s="89"/>
-      <c r="U26" s="89"/>
-      <c r="V26" s="89"/>
-      <c r="W26" s="89"/>
-      <c r="X26" s="89"/>
-      <c r="Y26" s="89"/>
-      <c r="Z26" s="89"/>
-      <c r="AA26" s="89"/>
-      <c r="AB26" s="89"/>
-      <c r="AC26" s="89"/>
-      <c r="AD26" s="89"/>
-      <c r="AE26" s="89"/>
-      <c r="AF26" s="89"/>
-      <c r="AG26" s="89"/>
-      <c r="AH26" s="89"/>
-      <c r="AI26" s="89"/>
-      <c r="AJ26" s="89"/>
-      <c r="AK26" s="89"/>
-      <c r="AL26" s="89"/>
+      <c r="A26" s="104"/>
+      <c r="B26" s="105"/>
+      <c r="C26" s="109"/>
+      <c r="D26" s="110"/>
+      <c r="E26" s="82"/>
+      <c r="F26" s="79"/>
+      <c r="G26" s="82"/>
+      <c r="H26" s="82"/>
+      <c r="I26" s="82"/>
+      <c r="J26" s="82"/>
+      <c r="K26" s="82"/>
+      <c r="L26" s="82"/>
+      <c r="M26" s="82"/>
+      <c r="N26" s="82"/>
+      <c r="O26" s="82"/>
+      <c r="P26" s="82"/>
+      <c r="Q26" s="82"/>
+      <c r="R26" s="82"/>
+      <c r="S26" s="82"/>
+      <c r="T26" s="82"/>
+      <c r="U26" s="82"/>
+      <c r="V26" s="82"/>
+      <c r="W26" s="82"/>
+      <c r="X26" s="82"/>
+      <c r="Y26" s="82"/>
+      <c r="Z26" s="82"/>
+      <c r="AA26" s="82"/>
+      <c r="AB26" s="82"/>
+      <c r="AC26" s="82"/>
+      <c r="AD26" s="82"/>
+      <c r="AE26" s="82"/>
+      <c r="AF26" s="82"/>
+      <c r="AG26" s="82"/>
+      <c r="AH26" s="82"/>
+      <c r="AI26" s="82"/>
+      <c r="AJ26" s="82"/>
+      <c r="AK26" s="82"/>
+      <c r="AL26" s="82"/>
     </row>
     <row r="27" spans="1:38" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="110"/>
-      <c r="B27" s="111"/>
-      <c r="C27" s="112"/>
-      <c r="D27" s="113"/>
-      <c r="E27" s="87"/>
-      <c r="F27" s="86"/>
-      <c r="G27" s="88"/>
-      <c r="H27" s="87"/>
-      <c r="I27" s="88"/>
-      <c r="J27" s="87"/>
-      <c r="K27" s="88"/>
-      <c r="L27" s="87"/>
-      <c r="M27" s="88"/>
-      <c r="N27" s="87"/>
-      <c r="O27" s="88"/>
-      <c r="P27" s="87"/>
-      <c r="Q27" s="88"/>
-      <c r="R27" s="87"/>
-      <c r="S27" s="88"/>
-      <c r="T27" s="87"/>
-      <c r="U27" s="88"/>
-      <c r="V27" s="87"/>
-      <c r="W27" s="88"/>
-      <c r="X27" s="87"/>
-      <c r="Y27" s="88"/>
-      <c r="Z27" s="87"/>
-      <c r="AA27" s="88"/>
-      <c r="AB27" s="87"/>
-      <c r="AC27" s="88"/>
-      <c r="AD27" s="87"/>
-      <c r="AE27" s="87"/>
-      <c r="AF27" s="87"/>
-      <c r="AG27" s="87"/>
-      <c r="AH27" s="87"/>
-      <c r="AI27" s="87"/>
-      <c r="AJ27" s="87"/>
-      <c r="AK27" s="87"/>
-      <c r="AL27" s="87"/>
+      <c r="A27" s="104"/>
+      <c r="B27" s="105"/>
+      <c r="C27" s="109"/>
+      <c r="D27" s="110"/>
+      <c r="E27" s="80"/>
+      <c r="F27" s="79"/>
+      <c r="G27" s="81"/>
+      <c r="H27" s="80"/>
+      <c r="I27" s="81"/>
+      <c r="J27" s="80"/>
+      <c r="K27" s="81"/>
+      <c r="L27" s="80"/>
+      <c r="M27" s="81"/>
+      <c r="N27" s="80"/>
+      <c r="O27" s="81"/>
+      <c r="P27" s="80"/>
+      <c r="Q27" s="81"/>
+      <c r="R27" s="80"/>
+      <c r="S27" s="81"/>
+      <c r="T27" s="80"/>
+      <c r="U27" s="81"/>
+      <c r="V27" s="80"/>
+      <c r="W27" s="81"/>
+      <c r="X27" s="80"/>
+      <c r="Y27" s="81"/>
+      <c r="Z27" s="80"/>
+      <c r="AA27" s="81"/>
+      <c r="AB27" s="80"/>
+      <c r="AC27" s="81"/>
+      <c r="AD27" s="80"/>
+      <c r="AE27" s="80"/>
+      <c r="AF27" s="80"/>
+      <c r="AG27" s="80"/>
+      <c r="AH27" s="80"/>
+      <c r="AI27" s="80"/>
+      <c r="AJ27" s="80"/>
+      <c r="AK27" s="80"/>
+      <c r="AL27" s="80"/>
     </row>
     <row r="28" spans="1:38" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="110"/>
-      <c r="B28" s="111"/>
-      <c r="C28" s="112"/>
-      <c r="D28" s="113"/>
-      <c r="E28" s="89"/>
-      <c r="F28" s="86"/>
-      <c r="G28" s="89"/>
-      <c r="H28" s="89"/>
-      <c r="I28" s="89"/>
-      <c r="J28" s="89"/>
-      <c r="K28" s="89"/>
-      <c r="L28" s="89"/>
-      <c r="M28" s="89"/>
-      <c r="N28" s="89"/>
-      <c r="O28" s="89"/>
-      <c r="P28" s="89"/>
-      <c r="Q28" s="89"/>
-      <c r="R28" s="89"/>
-      <c r="S28" s="89"/>
-      <c r="T28" s="89"/>
-      <c r="U28" s="89"/>
-      <c r="V28" s="89"/>
-      <c r="W28" s="89"/>
-      <c r="X28" s="89"/>
-      <c r="Y28" s="89"/>
-      <c r="Z28" s="89"/>
-      <c r="AA28" s="89"/>
-      <c r="AB28" s="89"/>
-      <c r="AC28" s="89"/>
-      <c r="AD28" s="89"/>
-      <c r="AE28" s="89"/>
-      <c r="AF28" s="89"/>
-      <c r="AG28" s="89"/>
-      <c r="AH28" s="89"/>
-      <c r="AI28" s="89"/>
-      <c r="AJ28" s="89"/>
-      <c r="AK28" s="89"/>
-      <c r="AL28" s="89"/>
+      <c r="A28" s="104"/>
+      <c r="B28" s="105"/>
+      <c r="C28" s="109"/>
+      <c r="D28" s="110"/>
+      <c r="E28" s="82"/>
+      <c r="F28" s="79"/>
+      <c r="G28" s="82"/>
+      <c r="H28" s="82"/>
+      <c r="I28" s="82"/>
+      <c r="J28" s="82"/>
+      <c r="K28" s="82"/>
+      <c r="L28" s="82"/>
+      <c r="M28" s="82"/>
+      <c r="N28" s="82"/>
+      <c r="O28" s="82"/>
+      <c r="P28" s="82"/>
+      <c r="Q28" s="82"/>
+      <c r="R28" s="82"/>
+      <c r="S28" s="82"/>
+      <c r="T28" s="82"/>
+      <c r="U28" s="82"/>
+      <c r="V28" s="82"/>
+      <c r="W28" s="82"/>
+      <c r="X28" s="82"/>
+      <c r="Y28" s="82"/>
+      <c r="Z28" s="82"/>
+      <c r="AA28" s="82"/>
+      <c r="AB28" s="82"/>
+      <c r="AC28" s="82"/>
+      <c r="AD28" s="82"/>
+      <c r="AE28" s="82"/>
+      <c r="AF28" s="82"/>
+      <c r="AG28" s="82"/>
+      <c r="AH28" s="82"/>
+      <c r="AI28" s="82"/>
+      <c r="AJ28" s="82"/>
+      <c r="AK28" s="82"/>
+      <c r="AL28" s="82"/>
     </row>
     <row r="29" spans="1:38" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="110"/>
-      <c r="B29" s="111"/>
-      <c r="C29" s="112"/>
-      <c r="D29" s="113"/>
-      <c r="E29" s="87"/>
-      <c r="F29" s="86"/>
-      <c r="G29" s="88"/>
-      <c r="H29" s="87"/>
-      <c r="I29" s="88"/>
-      <c r="J29" s="87"/>
-      <c r="K29" s="88"/>
-      <c r="L29" s="87"/>
-      <c r="M29" s="88"/>
-      <c r="N29" s="87"/>
-      <c r="O29" s="88"/>
-      <c r="P29" s="87"/>
-      <c r="Q29" s="88"/>
-      <c r="R29" s="87"/>
-      <c r="S29" s="88"/>
-      <c r="T29" s="87"/>
-      <c r="U29" s="88"/>
-      <c r="V29" s="87"/>
-      <c r="W29" s="88"/>
-      <c r="X29" s="87"/>
-      <c r="Y29" s="88"/>
-      <c r="Z29" s="87"/>
-      <c r="AA29" s="88"/>
-      <c r="AB29" s="87"/>
-      <c r="AC29" s="88"/>
-      <c r="AD29" s="87"/>
-      <c r="AE29" s="87"/>
-      <c r="AF29" s="87"/>
-      <c r="AG29" s="87"/>
-      <c r="AH29" s="87"/>
-      <c r="AI29" s="87"/>
-      <c r="AJ29" s="87"/>
-      <c r="AK29" s="87"/>
-      <c r="AL29" s="87"/>
+      <c r="A29" s="104"/>
+      <c r="B29" s="105"/>
+      <c r="C29" s="109"/>
+      <c r="D29" s="110"/>
+      <c r="E29" s="80"/>
+      <c r="F29" s="79"/>
+      <c r="G29" s="81"/>
+      <c r="H29" s="80"/>
+      <c r="I29" s="81"/>
+      <c r="J29" s="80"/>
+      <c r="K29" s="81"/>
+      <c r="L29" s="80"/>
+      <c r="M29" s="81"/>
+      <c r="N29" s="80"/>
+      <c r="O29" s="81"/>
+      <c r="P29" s="80"/>
+      <c r="Q29" s="81"/>
+      <c r="R29" s="80"/>
+      <c r="S29" s="81"/>
+      <c r="T29" s="80"/>
+      <c r="U29" s="81"/>
+      <c r="V29" s="80"/>
+      <c r="W29" s="81"/>
+      <c r="X29" s="80"/>
+      <c r="Y29" s="81"/>
+      <c r="Z29" s="80"/>
+      <c r="AA29" s="81"/>
+      <c r="AB29" s="80"/>
+      <c r="AC29" s="81"/>
+      <c r="AD29" s="80"/>
+      <c r="AE29" s="80"/>
+      <c r="AF29" s="80"/>
+      <c r="AG29" s="80"/>
+      <c r="AH29" s="80"/>
+      <c r="AI29" s="80"/>
+      <c r="AJ29" s="80"/>
+      <c r="AK29" s="80"/>
+      <c r="AL29" s="80"/>
     </row>
     <row r="30" spans="1:38" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="110"/>
-      <c r="B30" s="111"/>
-      <c r="C30" s="112"/>
-      <c r="D30" s="113"/>
-      <c r="E30" s="89"/>
-      <c r="F30" s="86"/>
-      <c r="G30" s="89"/>
-      <c r="H30" s="89"/>
-      <c r="I30" s="89"/>
-      <c r="J30" s="89"/>
-      <c r="K30" s="89"/>
-      <c r="L30" s="89"/>
-      <c r="M30" s="89"/>
-      <c r="N30" s="89"/>
-      <c r="O30" s="89"/>
-      <c r="P30" s="89"/>
-      <c r="Q30" s="89"/>
-      <c r="R30" s="89"/>
-      <c r="S30" s="89"/>
-      <c r="T30" s="89"/>
-      <c r="U30" s="89"/>
-      <c r="V30" s="89"/>
-      <c r="W30" s="89"/>
-      <c r="X30" s="89"/>
-      <c r="Y30" s="89"/>
-      <c r="Z30" s="89"/>
-      <c r="AA30" s="89"/>
-      <c r="AB30" s="89"/>
-      <c r="AC30" s="89"/>
-      <c r="AD30" s="89"/>
-      <c r="AE30" s="89"/>
-      <c r="AF30" s="89"/>
-      <c r="AG30" s="89"/>
-      <c r="AH30" s="89"/>
-      <c r="AI30" s="89"/>
-      <c r="AJ30" s="89"/>
-      <c r="AK30" s="89"/>
-      <c r="AL30" s="89"/>
+      <c r="A30" s="104"/>
+      <c r="B30" s="105"/>
+      <c r="C30" s="109"/>
+      <c r="D30" s="110"/>
+      <c r="E30" s="82"/>
+      <c r="F30" s="79"/>
+      <c r="G30" s="82"/>
+      <c r="H30" s="82"/>
+      <c r="I30" s="82"/>
+      <c r="J30" s="82"/>
+      <c r="K30" s="82"/>
+      <c r="L30" s="82"/>
+      <c r="M30" s="82"/>
+      <c r="N30" s="82"/>
+      <c r="O30" s="82"/>
+      <c r="P30" s="82"/>
+      <c r="Q30" s="82"/>
+      <c r="R30" s="82"/>
+      <c r="S30" s="82"/>
+      <c r="T30" s="82"/>
+      <c r="U30" s="82"/>
+      <c r="V30" s="82"/>
+      <c r="W30" s="82"/>
+      <c r="X30" s="82"/>
+      <c r="Y30" s="82"/>
+      <c r="Z30" s="82"/>
+      <c r="AA30" s="82"/>
+      <c r="AB30" s="82"/>
+      <c r="AC30" s="82"/>
+      <c r="AD30" s="82"/>
+      <c r="AE30" s="82"/>
+      <c r="AF30" s="82"/>
+      <c r="AG30" s="82"/>
+      <c r="AH30" s="82"/>
+      <c r="AI30" s="82"/>
+      <c r="AJ30" s="82"/>
+      <c r="AK30" s="82"/>
+      <c r="AL30" s="82"/>
     </row>
     <row r="31" spans="1:38" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="110"/>
-      <c r="B31" s="111"/>
-      <c r="C31" s="112"/>
-      <c r="D31" s="113"/>
-      <c r="E31" s="87"/>
-      <c r="F31" s="86"/>
-      <c r="G31" s="88"/>
-      <c r="H31" s="87"/>
-      <c r="I31" s="88"/>
-      <c r="J31" s="87"/>
-      <c r="K31" s="88"/>
-      <c r="L31" s="87"/>
-      <c r="M31" s="88"/>
-      <c r="N31" s="87"/>
-      <c r="O31" s="88"/>
-      <c r="P31" s="87"/>
-      <c r="Q31" s="88"/>
-      <c r="R31" s="87"/>
-      <c r="S31" s="88"/>
-      <c r="T31" s="87"/>
-      <c r="U31" s="88"/>
-      <c r="V31" s="87"/>
-      <c r="W31" s="88"/>
-      <c r="X31" s="87"/>
-      <c r="Y31" s="88"/>
-      <c r="Z31" s="87"/>
-      <c r="AA31" s="88"/>
-      <c r="AB31" s="87"/>
-      <c r="AC31" s="88"/>
-      <c r="AD31" s="87"/>
-      <c r="AE31" s="87"/>
-      <c r="AF31" s="87"/>
-      <c r="AG31" s="87"/>
-      <c r="AH31" s="87"/>
-      <c r="AI31" s="87"/>
-      <c r="AJ31" s="87"/>
-      <c r="AK31" s="87"/>
-      <c r="AL31" s="87"/>
+      <c r="A31" s="104"/>
+      <c r="B31" s="105"/>
+      <c r="C31" s="109"/>
+      <c r="D31" s="110"/>
+      <c r="E31" s="80"/>
+      <c r="F31" s="79"/>
+      <c r="G31" s="81"/>
+      <c r="H31" s="80"/>
+      <c r="I31" s="81"/>
+      <c r="J31" s="80"/>
+      <c r="K31" s="81"/>
+      <c r="L31" s="80"/>
+      <c r="M31" s="81"/>
+      <c r="N31" s="80"/>
+      <c r="O31" s="81"/>
+      <c r="P31" s="80"/>
+      <c r="Q31" s="81"/>
+      <c r="R31" s="80"/>
+      <c r="S31" s="81"/>
+      <c r="T31" s="80"/>
+      <c r="U31" s="81"/>
+      <c r="V31" s="80"/>
+      <c r="W31" s="81"/>
+      <c r="X31" s="80"/>
+      <c r="Y31" s="81"/>
+      <c r="Z31" s="80"/>
+      <c r="AA31" s="81"/>
+      <c r="AB31" s="80"/>
+      <c r="AC31" s="81"/>
+      <c r="AD31" s="80"/>
+      <c r="AE31" s="80"/>
+      <c r="AF31" s="80"/>
+      <c r="AG31" s="80"/>
+      <c r="AH31" s="80"/>
+      <c r="AI31" s="80"/>
+      <c r="AJ31" s="80"/>
+      <c r="AK31" s="80"/>
+      <c r="AL31" s="80"/>
     </row>
     <row r="32" spans="1:38" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="110"/>
-      <c r="B32" s="111"/>
-      <c r="C32" s="112"/>
-      <c r="D32" s="113"/>
-      <c r="E32" s="89"/>
-      <c r="F32" s="86"/>
-      <c r="G32" s="89"/>
-      <c r="H32" s="89"/>
-      <c r="I32" s="89"/>
-      <c r="J32" s="89"/>
-      <c r="K32" s="89"/>
-      <c r="L32" s="89"/>
-      <c r="M32" s="89"/>
-      <c r="N32" s="89"/>
-      <c r="O32" s="89"/>
-      <c r="P32" s="89"/>
-      <c r="Q32" s="89"/>
-      <c r="R32" s="89"/>
-      <c r="S32" s="89"/>
-      <c r="T32" s="89"/>
-      <c r="U32" s="89"/>
-      <c r="V32" s="89"/>
-      <c r="W32" s="89"/>
-      <c r="X32" s="89"/>
-      <c r="Y32" s="89"/>
-      <c r="Z32" s="89"/>
-      <c r="AA32" s="89"/>
-      <c r="AB32" s="89"/>
-      <c r="AC32" s="89"/>
-      <c r="AD32" s="89"/>
-      <c r="AE32" s="89"/>
-      <c r="AF32" s="89"/>
-      <c r="AG32" s="89"/>
-      <c r="AH32" s="89"/>
-      <c r="AI32" s="89"/>
-      <c r="AJ32" s="89"/>
-      <c r="AK32" s="89"/>
-      <c r="AL32" s="89"/>
+      <c r="A32" s="104"/>
+      <c r="B32" s="105"/>
+      <c r="C32" s="109"/>
+      <c r="D32" s="110"/>
+      <c r="E32" s="82"/>
+      <c r="F32" s="79"/>
+      <c r="G32" s="82"/>
+      <c r="H32" s="82"/>
+      <c r="I32" s="82"/>
+      <c r="J32" s="82"/>
+      <c r="K32" s="82"/>
+      <c r="L32" s="82"/>
+      <c r="M32" s="82"/>
+      <c r="N32" s="82"/>
+      <c r="O32" s="82"/>
+      <c r="P32" s="82"/>
+      <c r="Q32" s="82"/>
+      <c r="R32" s="82"/>
+      <c r="S32" s="82"/>
+      <c r="T32" s="82"/>
+      <c r="U32" s="82"/>
+      <c r="V32" s="82"/>
+      <c r="W32" s="82"/>
+      <c r="X32" s="82"/>
+      <c r="Y32" s="82"/>
+      <c r="Z32" s="82"/>
+      <c r="AA32" s="82"/>
+      <c r="AB32" s="82"/>
+      <c r="AC32" s="82"/>
+      <c r="AD32" s="82"/>
+      <c r="AE32" s="82"/>
+      <c r="AF32" s="82"/>
+      <c r="AG32" s="82"/>
+      <c r="AH32" s="82"/>
+      <c r="AI32" s="82"/>
+      <c r="AJ32" s="82"/>
+      <c r="AK32" s="82"/>
+      <c r="AL32" s="82"/>
     </row>
     <row r="33" spans="1:38" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="90"/>
-      <c r="B33" s="91"/>
-      <c r="C33" s="85"/>
-      <c r="D33" s="86"/>
-      <c r="E33" s="89"/>
-      <c r="F33" s="86"/>
-      <c r="G33" s="89"/>
-      <c r="H33" s="89"/>
-      <c r="I33" s="89"/>
-      <c r="J33" s="89"/>
-      <c r="K33" s="89"/>
-      <c r="L33" s="89"/>
-      <c r="M33" s="89"/>
-      <c r="N33" s="89"/>
-      <c r="O33" s="89"/>
-      <c r="P33" s="89"/>
-      <c r="Q33" s="89"/>
-      <c r="R33" s="89"/>
-      <c r="S33" s="89"/>
-      <c r="T33" s="89"/>
-      <c r="U33" s="89"/>
-      <c r="V33" s="89"/>
-      <c r="W33" s="89"/>
-      <c r="X33" s="89"/>
-      <c r="Y33" s="89"/>
-      <c r="Z33" s="89"/>
-      <c r="AA33" s="89"/>
-      <c r="AB33" s="89"/>
-      <c r="AC33" s="89"/>
-      <c r="AD33" s="89"/>
-      <c r="AE33" s="89"/>
-      <c r="AF33" s="89"/>
-      <c r="AG33" s="89"/>
-      <c r="AH33" s="89"/>
-      <c r="AI33" s="89"/>
-      <c r="AJ33" s="89"/>
-      <c r="AK33" s="89"/>
-      <c r="AL33" s="89"/>
+      <c r="A33" s="83"/>
+      <c r="B33" s="84"/>
+      <c r="C33" s="78"/>
+      <c r="D33" s="79"/>
+      <c r="E33" s="82"/>
+      <c r="F33" s="79"/>
+      <c r="G33" s="82"/>
+      <c r="H33" s="82"/>
+      <c r="I33" s="82"/>
+      <c r="J33" s="82"/>
+      <c r="K33" s="82"/>
+      <c r="L33" s="82"/>
+      <c r="M33" s="82"/>
+      <c r="N33" s="82"/>
+      <c r="O33" s="82"/>
+      <c r="P33" s="82"/>
+      <c r="Q33" s="82"/>
+      <c r="R33" s="82"/>
+      <c r="S33" s="82"/>
+      <c r="T33" s="82"/>
+      <c r="U33" s="82"/>
+      <c r="V33" s="82"/>
+      <c r="W33" s="82"/>
+      <c r="X33" s="82"/>
+      <c r="Y33" s="82"/>
+      <c r="Z33" s="82"/>
+      <c r="AA33" s="82"/>
+      <c r="AB33" s="82"/>
+      <c r="AC33" s="82"/>
+      <c r="AD33" s="82"/>
+      <c r="AE33" s="82"/>
+      <c r="AF33" s="82"/>
+      <c r="AG33" s="82"/>
+      <c r="AH33" s="82"/>
+      <c r="AI33" s="82"/>
+      <c r="AJ33" s="82"/>
+      <c r="AK33" s="82"/>
+      <c r="AL33" s="82"/>
     </row>
     <row r="34" spans="1:38" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="90"/>
-      <c r="B34" s="91"/>
-      <c r="C34" s="85"/>
-      <c r="D34" s="86"/>
-      <c r="E34" s="89"/>
-      <c r="F34" s="86"/>
-      <c r="G34" s="89"/>
-      <c r="H34" s="89"/>
-      <c r="I34" s="89"/>
-      <c r="J34" s="89"/>
-      <c r="K34" s="89"/>
-      <c r="L34" s="89"/>
-      <c r="M34" s="89"/>
-      <c r="N34" s="89"/>
-      <c r="O34" s="89"/>
-      <c r="P34" s="89"/>
-      <c r="Q34" s="89"/>
-      <c r="R34" s="89"/>
-      <c r="S34" s="89"/>
-      <c r="T34" s="89"/>
-      <c r="U34" s="89"/>
-      <c r="V34" s="89"/>
-      <c r="W34" s="89"/>
-      <c r="X34" s="89"/>
-      <c r="Y34" s="89"/>
-      <c r="Z34" s="89"/>
-      <c r="AA34" s="89"/>
-      <c r="AB34" s="89"/>
-      <c r="AC34" s="89"/>
-      <c r="AD34" s="89"/>
-      <c r="AE34" s="89"/>
-      <c r="AF34" s="89"/>
-      <c r="AG34" s="89"/>
-      <c r="AH34" s="89"/>
-      <c r="AI34" s="89"/>
-      <c r="AJ34" s="89"/>
-      <c r="AK34" s="89"/>
-      <c r="AL34" s="89"/>
+      <c r="A34" s="83"/>
+      <c r="B34" s="84"/>
+      <c r="C34" s="78"/>
+      <c r="D34" s="79"/>
+      <c r="E34" s="82"/>
+      <c r="F34" s="79"/>
+      <c r="G34" s="82"/>
+      <c r="H34" s="82"/>
+      <c r="I34" s="82"/>
+      <c r="J34" s="82"/>
+      <c r="K34" s="82"/>
+      <c r="L34" s="82"/>
+      <c r="M34" s="82"/>
+      <c r="N34" s="82"/>
+      <c r="O34" s="82"/>
+      <c r="P34" s="82"/>
+      <c r="Q34" s="82"/>
+      <c r="R34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="82"/>
+      <c r="V34" s="82"/>
+      <c r="W34" s="82"/>
+      <c r="X34" s="82"/>
+      <c r="Y34" s="82"/>
+      <c r="Z34" s="82"/>
+      <c r="AA34" s="82"/>
+      <c r="AB34" s="82"/>
+      <c r="AC34" s="82"/>
+      <c r="AD34" s="82"/>
+      <c r="AE34" s="82"/>
+      <c r="AF34" s="82"/>
+      <c r="AG34" s="82"/>
+      <c r="AH34" s="82"/>
+      <c r="AI34" s="82"/>
+      <c r="AJ34" s="82"/>
+      <c r="AK34" s="82"/>
+      <c r="AL34" s="82"/>
     </row>
     <row r="35" spans="1:38" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="90"/>
-      <c r="B35" s="91"/>
-      <c r="C35" s="85"/>
-      <c r="D35" s="86"/>
-      <c r="E35" s="89"/>
-      <c r="F35" s="86"/>
-      <c r="G35" s="89"/>
-      <c r="H35" s="89"/>
-      <c r="I35" s="89"/>
-      <c r="J35" s="89"/>
-      <c r="K35" s="89"/>
-      <c r="L35" s="89"/>
-      <c r="M35" s="89"/>
-      <c r="N35" s="89"/>
-      <c r="O35" s="89"/>
-      <c r="P35" s="89"/>
-      <c r="Q35" s="89"/>
-      <c r="R35" s="89"/>
-      <c r="S35" s="89"/>
-      <c r="T35" s="89"/>
-      <c r="U35" s="89"/>
-      <c r="V35" s="89"/>
-      <c r="W35" s="89"/>
-      <c r="X35" s="89"/>
-      <c r="Y35" s="89"/>
-      <c r="Z35" s="89"/>
-      <c r="AA35" s="89"/>
-      <c r="AB35" s="89"/>
-      <c r="AC35" s="89"/>
-      <c r="AD35" s="89"/>
-      <c r="AE35" s="89"/>
-      <c r="AF35" s="89"/>
-      <c r="AG35" s="89"/>
-      <c r="AH35" s="89"/>
-      <c r="AI35" s="89"/>
-      <c r="AJ35" s="89"/>
-      <c r="AK35" s="89"/>
-      <c r="AL35" s="89"/>
+      <c r="A35" s="83"/>
+      <c r="B35" s="84"/>
+      <c r="C35" s="78"/>
+      <c r="D35" s="79"/>
+      <c r="E35" s="82"/>
+      <c r="F35" s="79"/>
+      <c r="G35" s="82"/>
+      <c r="H35" s="82"/>
+      <c r="I35" s="82"/>
+      <c r="J35" s="82"/>
+      <c r="K35" s="82"/>
+      <c r="L35" s="82"/>
+      <c r="M35" s="82"/>
+      <c r="N35" s="82"/>
+      <c r="O35" s="82"/>
+      <c r="P35" s="82"/>
+      <c r="Q35" s="82"/>
+      <c r="R35" s="82"/>
+      <c r="S35" s="82"/>
+      <c r="T35" s="82"/>
+      <c r="U35" s="82"/>
+      <c r="V35" s="82"/>
+      <c r="W35" s="82"/>
+      <c r="X35" s="82"/>
+      <c r="Y35" s="82"/>
+      <c r="Z35" s="82"/>
+      <c r="AA35" s="82"/>
+      <c r="AB35" s="82"/>
+      <c r="AC35" s="82"/>
+      <c r="AD35" s="82"/>
+      <c r="AE35" s="82"/>
+      <c r="AF35" s="82"/>
+      <c r="AG35" s="82"/>
+      <c r="AH35" s="82"/>
+      <c r="AI35" s="82"/>
+      <c r="AJ35" s="82"/>
+      <c r="AK35" s="82"/>
+      <c r="AL35" s="82"/>
     </row>
     <row r="36" spans="1:38" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="90"/>
-      <c r="B36" s="91"/>
-      <c r="C36" s="85"/>
-      <c r="D36" s="86"/>
-      <c r="E36" s="89"/>
-      <c r="F36" s="86"/>
-      <c r="G36" s="89"/>
-      <c r="H36" s="89"/>
-      <c r="I36" s="89"/>
-      <c r="J36" s="89"/>
-      <c r="K36" s="89"/>
-      <c r="L36" s="89"/>
-      <c r="M36" s="89"/>
-      <c r="N36" s="89"/>
-      <c r="O36" s="89"/>
-      <c r="P36" s="89"/>
-      <c r="Q36" s="89"/>
-      <c r="R36" s="89"/>
-      <c r="S36" s="89"/>
-      <c r="T36" s="89"/>
-      <c r="U36" s="89"/>
-      <c r="V36" s="89"/>
-      <c r="W36" s="89"/>
-      <c r="X36" s="89"/>
-      <c r="Y36" s="89"/>
-      <c r="Z36" s="89"/>
-      <c r="AA36" s="89"/>
-      <c r="AB36" s="89"/>
-      <c r="AC36" s="89"/>
-      <c r="AD36" s="89"/>
-      <c r="AE36" s="89"/>
-      <c r="AF36" s="89"/>
-      <c r="AG36" s="89"/>
-      <c r="AH36" s="89"/>
-      <c r="AI36" s="89"/>
-      <c r="AJ36" s="89"/>
-      <c r="AK36" s="89"/>
-      <c r="AL36" s="89"/>
+      <c r="A36" s="83"/>
+      <c r="B36" s="84"/>
+      <c r="C36" s="78"/>
+      <c r="D36" s="79"/>
+      <c r="E36" s="82"/>
+      <c r="F36" s="79"/>
+      <c r="G36" s="82"/>
+      <c r="H36" s="82"/>
+      <c r="I36" s="82"/>
+      <c r="J36" s="82"/>
+      <c r="K36" s="82"/>
+      <c r="L36" s="82"/>
+      <c r="M36" s="82"/>
+      <c r="N36" s="82"/>
+      <c r="O36" s="82"/>
+      <c r="P36" s="82"/>
+      <c r="Q36" s="82"/>
+      <c r="R36" s="82"/>
+      <c r="S36" s="82"/>
+      <c r="T36" s="82"/>
+      <c r="U36" s="82"/>
+      <c r="V36" s="82"/>
+      <c r="W36" s="82"/>
+      <c r="X36" s="82"/>
+      <c r="Y36" s="82"/>
+      <c r="Z36" s="82"/>
+      <c r="AA36" s="82"/>
+      <c r="AB36" s="82"/>
+      <c r="AC36" s="82"/>
+      <c r="AD36" s="82"/>
+      <c r="AE36" s="82"/>
+      <c r="AF36" s="82"/>
+      <c r="AG36" s="82"/>
+      <c r="AH36" s="82"/>
+      <c r="AI36" s="82"/>
+      <c r="AJ36" s="82"/>
+      <c r="AK36" s="82"/>
+      <c r="AL36" s="82"/>
     </row>
     <row r="37" spans="1:38" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="90"/>
-      <c r="B37" s="91"/>
-      <c r="C37" s="85"/>
-      <c r="D37" s="86"/>
-      <c r="E37" s="89"/>
-      <c r="F37" s="86"/>
-      <c r="G37" s="89"/>
-      <c r="H37" s="89"/>
-      <c r="I37" s="89"/>
-      <c r="J37" s="89"/>
-      <c r="K37" s="89"/>
-      <c r="L37" s="89"/>
-      <c r="M37" s="89"/>
-      <c r="N37" s="89"/>
-      <c r="O37" s="89"/>
-      <c r="P37" s="89"/>
-      <c r="Q37" s="89"/>
-      <c r="R37" s="89"/>
-      <c r="S37" s="89"/>
-      <c r="T37" s="89"/>
-      <c r="U37" s="89"/>
-      <c r="V37" s="89"/>
-      <c r="W37" s="89"/>
-      <c r="X37" s="89"/>
-      <c r="Y37" s="89"/>
-      <c r="Z37" s="89"/>
-      <c r="AA37" s="89"/>
-      <c r="AB37" s="89"/>
-      <c r="AC37" s="89"/>
-      <c r="AD37" s="89"/>
-      <c r="AE37" s="89"/>
-      <c r="AF37" s="89"/>
-      <c r="AG37" s="89"/>
-      <c r="AH37" s="89"/>
-      <c r="AI37" s="89"/>
-      <c r="AJ37" s="89"/>
-      <c r="AK37" s="89"/>
-      <c r="AL37" s="89"/>
+      <c r="A37" s="83"/>
+      <c r="B37" s="84"/>
+      <c r="C37" s="78"/>
+      <c r="D37" s="79"/>
+      <c r="E37" s="82"/>
+      <c r="F37" s="79"/>
+      <c r="G37" s="82"/>
+      <c r="H37" s="82"/>
+      <c r="I37" s="82"/>
+      <c r="J37" s="82"/>
+      <c r="K37" s="82"/>
+      <c r="L37" s="82"/>
+      <c r="M37" s="82"/>
+      <c r="N37" s="82"/>
+      <c r="O37" s="82"/>
+      <c r="P37" s="82"/>
+      <c r="Q37" s="82"/>
+      <c r="R37" s="82"/>
+      <c r="S37" s="82"/>
+      <c r="T37" s="82"/>
+      <c r="U37" s="82"/>
+      <c r="V37" s="82"/>
+      <c r="W37" s="82"/>
+      <c r="X37" s="82"/>
+      <c r="Y37" s="82"/>
+      <c r="Z37" s="82"/>
+      <c r="AA37" s="82"/>
+      <c r="AB37" s="82"/>
+      <c r="AC37" s="82"/>
+      <c r="AD37" s="82"/>
+      <c r="AE37" s="82"/>
+      <c r="AF37" s="82"/>
+      <c r="AG37" s="82"/>
+      <c r="AH37" s="82"/>
+      <c r="AI37" s="82"/>
+      <c r="AJ37" s="82"/>
+      <c r="AK37" s="82"/>
+      <c r="AL37" s="82"/>
     </row>
     <row r="38" spans="1:38" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="90"/>
-      <c r="B38" s="91"/>
-      <c r="C38" s="85"/>
-      <c r="D38" s="86"/>
-      <c r="E38" s="89"/>
-      <c r="F38" s="86"/>
-      <c r="G38" s="89"/>
-      <c r="H38" s="89"/>
-      <c r="I38" s="89"/>
-      <c r="J38" s="89"/>
-      <c r="K38" s="89"/>
-      <c r="L38" s="89"/>
-      <c r="M38" s="89"/>
-      <c r="N38" s="89"/>
-      <c r="O38" s="89"/>
-      <c r="P38" s="89"/>
-      <c r="Q38" s="89"/>
-      <c r="R38" s="89"/>
-      <c r="S38" s="89"/>
-      <c r="T38" s="89"/>
-      <c r="U38" s="89"/>
-      <c r="V38" s="89"/>
-      <c r="W38" s="89"/>
-      <c r="X38" s="89"/>
-      <c r="Y38" s="89"/>
-      <c r="Z38" s="89"/>
-      <c r="AA38" s="89"/>
-      <c r="AB38" s="89"/>
-      <c r="AC38" s="89"/>
-      <c r="AD38" s="89"/>
-      <c r="AE38" s="89"/>
-      <c r="AF38" s="89"/>
-      <c r="AG38" s="89"/>
-      <c r="AH38" s="89"/>
-      <c r="AI38" s="89"/>
-      <c r="AJ38" s="89"/>
-      <c r="AK38" s="89"/>
-      <c r="AL38" s="89"/>
+      <c r="A38" s="83"/>
+      <c r="B38" s="84"/>
+      <c r="C38" s="78"/>
+      <c r="D38" s="79"/>
+      <c r="E38" s="82"/>
+      <c r="F38" s="79"/>
+      <c r="G38" s="82"/>
+      <c r="H38" s="82"/>
+      <c r="I38" s="82"/>
+      <c r="J38" s="82"/>
+      <c r="K38" s="82"/>
+      <c r="L38" s="82"/>
+      <c r="M38" s="82"/>
+      <c r="N38" s="82"/>
+      <c r="O38" s="82"/>
+      <c r="P38" s="82"/>
+      <c r="Q38" s="82"/>
+      <c r="R38" s="82"/>
+      <c r="S38" s="82"/>
+      <c r="T38" s="82"/>
+      <c r="U38" s="82"/>
+      <c r="V38" s="82"/>
+      <c r="W38" s="82"/>
+      <c r="X38" s="82"/>
+      <c r="Y38" s="82"/>
+      <c r="Z38" s="82"/>
+      <c r="AA38" s="82"/>
+      <c r="AB38" s="82"/>
+      <c r="AC38" s="82"/>
+      <c r="AD38" s="82"/>
+      <c r="AE38" s="82"/>
+      <c r="AF38" s="82"/>
+      <c r="AG38" s="82"/>
+      <c r="AH38" s="82"/>
+      <c r="AI38" s="82"/>
+      <c r="AJ38" s="82"/>
+      <c r="AK38" s="82"/>
+      <c r="AL38" s="82"/>
     </row>
     <row r="39" spans="1:38" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="110"/>
-      <c r="B39" s="111"/>
-      <c r="C39" s="112"/>
-      <c r="D39" s="113"/>
-      <c r="E39" s="87"/>
-      <c r="F39" s="86"/>
-      <c r="G39" s="88"/>
-      <c r="H39" s="87"/>
-      <c r="I39" s="88"/>
-      <c r="J39" s="87"/>
-      <c r="K39" s="88"/>
-      <c r="L39" s="87"/>
-      <c r="M39" s="88"/>
-      <c r="N39" s="87"/>
-      <c r="O39" s="88"/>
-      <c r="P39" s="87"/>
-      <c r="Q39" s="88"/>
-      <c r="R39" s="87"/>
-      <c r="S39" s="88"/>
-      <c r="T39" s="87"/>
-      <c r="U39" s="88"/>
-      <c r="V39" s="87"/>
-      <c r="W39" s="88"/>
-      <c r="X39" s="87"/>
-      <c r="Y39" s="88"/>
-      <c r="Z39" s="87"/>
-      <c r="AA39" s="88"/>
-      <c r="AB39" s="87"/>
-      <c r="AC39" s="88"/>
-      <c r="AD39" s="87"/>
-      <c r="AE39" s="87"/>
-      <c r="AF39" s="87"/>
-      <c r="AG39" s="87"/>
-      <c r="AH39" s="87"/>
-      <c r="AI39" s="87"/>
-      <c r="AJ39" s="87"/>
-      <c r="AK39" s="87"/>
-      <c r="AL39" s="87"/>
+      <c r="A39" s="104"/>
+      <c r="B39" s="105"/>
+      <c r="C39" s="109"/>
+      <c r="D39" s="110"/>
+      <c r="E39" s="80"/>
+      <c r="F39" s="79"/>
+      <c r="G39" s="81"/>
+      <c r="H39" s="80"/>
+      <c r="I39" s="81"/>
+      <c r="J39" s="80"/>
+      <c r="K39" s="81"/>
+      <c r="L39" s="80"/>
+      <c r="M39" s="81"/>
+      <c r="N39" s="80"/>
+      <c r="O39" s="81"/>
+      <c r="P39" s="80"/>
+      <c r="Q39" s="81"/>
+      <c r="R39" s="80"/>
+      <c r="S39" s="81"/>
+      <c r="T39" s="80"/>
+      <c r="U39" s="81"/>
+      <c r="V39" s="80"/>
+      <c r="W39" s="81"/>
+      <c r="X39" s="80"/>
+      <c r="Y39" s="81"/>
+      <c r="Z39" s="80"/>
+      <c r="AA39" s="81"/>
+      <c r="AB39" s="80"/>
+      <c r="AC39" s="81"/>
+      <c r="AD39" s="80"/>
+      <c r="AE39" s="80"/>
+      <c r="AF39" s="80"/>
+      <c r="AG39" s="80"/>
+      <c r="AH39" s="80"/>
+      <c r="AI39" s="80"/>
+      <c r="AJ39" s="80"/>
+      <c r="AK39" s="80"/>
+      <c r="AL39" s="80"/>
     </row>
     <row r="40" spans="1:38" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="110"/>
-      <c r="B40" s="111"/>
-      <c r="C40" s="112"/>
-      <c r="D40" s="113"/>
-      <c r="E40" s="89"/>
-      <c r="F40" s="86"/>
-      <c r="G40" s="89"/>
-      <c r="H40" s="89"/>
-      <c r="I40" s="89"/>
-      <c r="J40" s="89"/>
-      <c r="K40" s="89"/>
-      <c r="L40" s="89"/>
-      <c r="M40" s="89"/>
-      <c r="N40" s="89"/>
-      <c r="O40" s="89"/>
-      <c r="P40" s="89"/>
-      <c r="Q40" s="89"/>
-      <c r="R40" s="89"/>
-      <c r="S40" s="89"/>
-      <c r="T40" s="89"/>
-      <c r="U40" s="89"/>
-      <c r="V40" s="89"/>
-      <c r="W40" s="89"/>
-      <c r="X40" s="89"/>
-      <c r="Y40" s="89"/>
-      <c r="Z40" s="89"/>
-      <c r="AA40" s="89"/>
-      <c r="AB40" s="89"/>
-      <c r="AC40" s="89"/>
-      <c r="AD40" s="89"/>
-      <c r="AE40" s="89"/>
-      <c r="AF40" s="89"/>
-      <c r="AG40" s="89"/>
-      <c r="AH40" s="89"/>
-      <c r="AI40" s="89"/>
-      <c r="AJ40" s="89"/>
-      <c r="AK40" s="89"/>
-      <c r="AL40" s="89"/>
+      <c r="A40" s="104"/>
+      <c r="B40" s="105"/>
+      <c r="C40" s="109"/>
+      <c r="D40" s="110"/>
+      <c r="E40" s="82"/>
+      <c r="F40" s="79"/>
+      <c r="G40" s="82"/>
+      <c r="H40" s="82"/>
+      <c r="I40" s="82"/>
+      <c r="J40" s="82"/>
+      <c r="K40" s="82"/>
+      <c r="L40" s="82"/>
+      <c r="M40" s="82"/>
+      <c r="N40" s="82"/>
+      <c r="O40" s="82"/>
+      <c r="P40" s="82"/>
+      <c r="Q40" s="82"/>
+      <c r="R40" s="82"/>
+      <c r="S40" s="82"/>
+      <c r="T40" s="82"/>
+      <c r="U40" s="82"/>
+      <c r="V40" s="82"/>
+      <c r="W40" s="82"/>
+      <c r="X40" s="82"/>
+      <c r="Y40" s="82"/>
+      <c r="Z40" s="82"/>
+      <c r="AA40" s="82"/>
+      <c r="AB40" s="82"/>
+      <c r="AC40" s="82"/>
+      <c r="AD40" s="82"/>
+      <c r="AE40" s="82"/>
+      <c r="AF40" s="82"/>
+      <c r="AG40" s="82"/>
+      <c r="AH40" s="82"/>
+      <c r="AI40" s="82"/>
+      <c r="AJ40" s="82"/>
+      <c r="AK40" s="82"/>
+      <c r="AL40" s="82"/>
     </row>
     <row r="41" spans="1:38" s="3" customFormat="1" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="137"/>
-      <c r="B41" s="138"/>
-      <c r="C41" s="139"/>
-      <c r="D41" s="140"/>
-      <c r="E41" s="92"/>
-      <c r="F41" s="93"/>
-      <c r="G41" s="92"/>
-      <c r="H41" s="92"/>
-      <c r="I41" s="92"/>
-      <c r="J41" s="92"/>
-      <c r="K41" s="92"/>
-      <c r="L41" s="92"/>
-      <c r="M41" s="92"/>
-      <c r="N41" s="92"/>
-      <c r="O41" s="92"/>
-      <c r="P41" s="92"/>
-      <c r="Q41" s="92"/>
-      <c r="R41" s="92"/>
-      <c r="S41" s="92"/>
-      <c r="T41" s="92"/>
-      <c r="U41" s="92"/>
-      <c r="V41" s="92"/>
-      <c r="W41" s="92"/>
-      <c r="X41" s="92"/>
-      <c r="Y41" s="92"/>
-      <c r="Z41" s="92"/>
-      <c r="AA41" s="92"/>
-      <c r="AB41" s="92"/>
-      <c r="AC41" s="92"/>
-      <c r="AD41" s="92"/>
-      <c r="AE41" s="92"/>
-      <c r="AF41" s="92"/>
-      <c r="AG41" s="92"/>
-      <c r="AH41" s="92"/>
-      <c r="AI41" s="92"/>
-      <c r="AJ41" s="92"/>
-      <c r="AK41" s="92"/>
-      <c r="AL41" s="92"/>
+      <c r="A41" s="102"/>
+      <c r="B41" s="103"/>
+      <c r="C41" s="106"/>
+      <c r="D41" s="107"/>
+      <c r="E41" s="85"/>
+      <c r="F41" s="86"/>
+      <c r="G41" s="85"/>
+      <c r="H41" s="85"/>
+      <c r="I41" s="85"/>
+      <c r="J41" s="85"/>
+      <c r="K41" s="85"/>
+      <c r="L41" s="85"/>
+      <c r="M41" s="85"/>
+      <c r="N41" s="85"/>
+      <c r="O41" s="85"/>
+      <c r="P41" s="85"/>
+      <c r="Q41" s="85"/>
+      <c r="R41" s="85"/>
+      <c r="S41" s="85"/>
+      <c r="T41" s="85"/>
+      <c r="U41" s="85"/>
+      <c r="V41" s="85"/>
+      <c r="W41" s="85"/>
+      <c r="X41" s="85"/>
+      <c r="Y41" s="85"/>
+      <c r="Z41" s="85"/>
+      <c r="AA41" s="85"/>
+      <c r="AB41" s="85"/>
+      <c r="AC41" s="85"/>
+      <c r="AD41" s="85"/>
+      <c r="AE41" s="85"/>
+      <c r="AF41" s="85"/>
+      <c r="AG41" s="85"/>
+      <c r="AH41" s="85"/>
+      <c r="AI41" s="85"/>
+      <c r="AJ41" s="85"/>
+      <c r="AK41" s="85"/>
+      <c r="AL41" s="85"/>
     </row>
     <row r="42" spans="1:38" s="3" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="75" t="s">
+      <c r="A42" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="B42" s="54"/>
-      <c r="C42" s="55"/>
-      <c r="D42" s="55"/>
-      <c r="E42" s="55"/>
-      <c r="F42" s="76" t="s">
+      <c r="B42" s="49"/>
+      <c r="C42" s="50"/>
+      <c r="D42" s="50"/>
+      <c r="E42" s="50"/>
+      <c r="F42" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="G42" s="77"/>
-      <c r="H42" s="56"/>
-      <c r="I42" s="56"/>
-      <c r="J42" s="56"/>
-      <c r="K42" s="56"/>
-      <c r="L42" s="56"/>
-      <c r="M42" s="56"/>
-      <c r="N42" s="56"/>
-      <c r="O42" s="56"/>
-      <c r="P42" s="56"/>
-      <c r="Q42" s="56"/>
-      <c r="R42" s="56"/>
-      <c r="S42" s="56"/>
-      <c r="T42" s="56"/>
-      <c r="U42" s="56"/>
-      <c r="V42" s="56"/>
-      <c r="W42" s="56"/>
-      <c r="X42" s="56"/>
-      <c r="Y42" s="56"/>
-      <c r="Z42" s="56"/>
-      <c r="AA42" s="56"/>
-      <c r="AB42" s="56"/>
-      <c r="AC42" s="56"/>
-      <c r="AD42" s="56"/>
-      <c r="AE42" s="56"/>
-      <c r="AF42" s="56"/>
-      <c r="AG42" s="56"/>
-      <c r="AH42" s="56"/>
-      <c r="AI42" s="56"/>
-      <c r="AJ42" s="56"/>
-      <c r="AK42" s="56"/>
-      <c r="AL42" s="56"/>
+      <c r="G42" s="72"/>
+      <c r="H42" s="51"/>
+      <c r="I42" s="51"/>
+      <c r="J42" s="51"/>
+      <c r="K42" s="51"/>
+      <c r="L42" s="51"/>
+      <c r="M42" s="51"/>
+      <c r="N42" s="51"/>
+      <c r="O42" s="51"/>
+      <c r="P42" s="51"/>
+      <c r="Q42" s="51"/>
+      <c r="R42" s="51"/>
+      <c r="S42" s="51"/>
+      <c r="T42" s="51"/>
+      <c r="U42" s="51"/>
+      <c r="V42" s="51"/>
+      <c r="W42" s="51"/>
+      <c r="X42" s="51"/>
+      <c r="Y42" s="51"/>
+      <c r="Z42" s="51"/>
+      <c r="AA42" s="51"/>
+      <c r="AB42" s="51"/>
+      <c r="AC42" s="51"/>
+      <c r="AD42" s="51"/>
+      <c r="AE42" s="51"/>
+      <c r="AF42" s="51"/>
+      <c r="AG42" s="51"/>
+      <c r="AH42" s="51"/>
+      <c r="AI42" s="51"/>
+      <c r="AJ42" s="51"/>
+      <c r="AK42" s="51"/>
+      <c r="AL42" s="51"/>
     </row>
     <row r="43" spans="1:38" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="11"/>
@@ -4875,89 +4851,47 @@
       <c r="B44" s="12"/>
     </row>
     <row r="45" spans="1:38" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="134"/>
-      <c r="B45" s="134"/>
-      <c r="C45" s="134"/>
-      <c r="D45" s="134"/>
-      <c r="E45" s="134"/>
-      <c r="F45" s="134"/>
-      <c r="G45" s="134"/>
-      <c r="H45" s="134"/>
-      <c r="I45" s="134"/>
-      <c r="J45" s="134"/>
-      <c r="K45" s="134"/>
-      <c r="L45" s="134"/>
-      <c r="M45" s="134"/>
-      <c r="N45" s="134"/>
-      <c r="O45" s="134"/>
-      <c r="P45" s="134"/>
-      <c r="Q45" s="134"/>
-      <c r="R45" s="134"/>
-      <c r="S45" s="134"/>
-      <c r="T45" s="134"/>
-      <c r="U45" s="134"/>
-      <c r="V45" s="134"/>
-      <c r="W45" s="134"/>
-      <c r="X45" s="134"/>
-      <c r="Y45" s="134"/>
-      <c r="Z45" s="134"/>
-      <c r="AA45" s="134"/>
-      <c r="AB45" s="134"/>
-      <c r="AC45" s="134"/>
-      <c r="AD45" s="134"/>
-      <c r="AE45" s="134"/>
-      <c r="AF45" s="134"/>
-      <c r="AG45" s="134"/>
-      <c r="AH45" s="134"/>
-      <c r="AI45" s="134"/>
-      <c r="AJ45" s="134"/>
-      <c r="AK45" s="134"/>
-      <c r="AL45" s="134"/>
+      <c r="A45" s="108"/>
+      <c r="B45" s="108"/>
+      <c r="C45" s="108"/>
+      <c r="D45" s="108"/>
+      <c r="E45" s="108"/>
+      <c r="F45" s="108"/>
+      <c r="G45" s="108"/>
+      <c r="H45" s="108"/>
+      <c r="I45" s="108"/>
+      <c r="J45" s="108"/>
+      <c r="K45" s="108"/>
+      <c r="L45" s="108"/>
+      <c r="M45" s="108"/>
+      <c r="N45" s="108"/>
+      <c r="O45" s="108"/>
+      <c r="P45" s="108"/>
+      <c r="Q45" s="108"/>
+      <c r="R45" s="108"/>
+      <c r="S45" s="108"/>
+      <c r="T45" s="108"/>
+      <c r="U45" s="108"/>
+      <c r="V45" s="108"/>
+      <c r="W45" s="108"/>
+      <c r="X45" s="108"/>
+      <c r="Y45" s="108"/>
+      <c r="Z45" s="108"/>
+      <c r="AA45" s="108"/>
+      <c r="AB45" s="108"/>
+      <c r="AC45" s="108"/>
+      <c r="AD45" s="108"/>
+      <c r="AE45" s="108"/>
+      <c r="AF45" s="108"/>
+      <c r="AG45" s="108"/>
+      <c r="AH45" s="108"/>
+      <c r="AI45" s="108"/>
+      <c r="AJ45" s="108"/>
+      <c r="AK45" s="108"/>
+      <c r="AL45" s="108"/>
     </row>
   </sheetData>
   <mergeCells count="54">
-    <mergeCell ref="A10:B11"/>
-    <mergeCell ref="C10:AL10"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A45:AL45"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="AI6:AJ6"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="F1:AJ4"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="A1:D4"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F8:AL8"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C29:D29"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="A40:B40"/>
@@ -4970,6 +4904,48 @@
     <mergeCell ref="C32:D32"/>
     <mergeCell ref="A39:B39"/>
     <mergeCell ref="C39:D39"/>
+    <mergeCell ref="AI6:AJ6"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="F1:AJ4"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="A1:D4"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F8:AL8"/>
+    <mergeCell ref="A45:AL45"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A10:B11"/>
+    <mergeCell ref="C10:AL10"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C29:D29"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <dataValidations count="1">
@@ -4979,7 +4955,7 @@
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.59055118110236227" bottom="0" header="0" footer="0"/>
-  <pageSetup paperSize="274" scale="33" orientation="landscape" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <pageSetup paperSize="274" scale="31" orientation="landscape" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId2"/>
 </worksheet>
